--- a/public/exports/29189366.xlsx
+++ b/public/exports/29189366.xlsx
@@ -181,16 +181,16 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1352702</t>
+          <t xml:space="preserve">253097, 253098</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F4">
-        <v>270</v>
+        <v>579</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -231,16 +231,16 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">5327777</t>
+          <t xml:space="preserve">255560, 255561</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F5">
-        <v>2217</v>
+        <v>4613</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -281,16 +281,16 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">5328529, 100965431</t>
+          <t xml:space="preserve">257561</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F6">
-        <v>1368</v>
+        <v>1949</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -331,16 +331,16 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">5329943</t>
+          <t xml:space="preserve">5327777</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="F7">
-        <v>427</v>
+        <v>2217</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -381,16 +381,16 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">5329943</t>
+          <t xml:space="preserve">5328529, 100965431</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F8">
-        <v>553</v>
+        <v>1368</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -436,11 +436,11 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F9">
-        <v>553</v>
+        <v>427</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -486,7 +486,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F10">
@@ -536,11 +536,11 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F11">
-        <v>427</v>
+        <v>553</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -586,11 +586,11 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="F12">
-        <v>2384</v>
+        <v>553</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -636,11 +636,11 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F13">
-        <v>270</v>
+        <v>427</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -686,11 +686,11 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F14">
-        <v>1056</v>
+        <v>2384</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -736,11 +736,11 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="F15">
-        <v>989</v>
+        <v>270</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -786,11 +786,11 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F16">
-        <v>989</v>
+        <v>1056</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F17">
@@ -881,16 +881,16 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">717923, 10036947</t>
+          <t xml:space="preserve">5329943</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F18">
-        <v>8327</v>
+        <v>989</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -931,16 +931,16 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">717932, 2261588</t>
+          <t xml:space="preserve">5329943</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F19">
-        <v>2285</v>
+        <v>989</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -981,16 +981,16 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">9065689, 100730166</t>
+          <t xml:space="preserve">717932, 2261588</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F20">
-        <v>8999</v>
+        <v>2285</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1031,35 +1031,35 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">5329943</t>
+          <t xml:space="preserve">717923, 10036947</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F21">
-        <v>2581</v>
+        <v>8327</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">311220566</t>
+          <t xml:space="preserve">200056514</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-03</t>
+          <t xml:space="preserve">2022-01-08</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -1081,25 +1081,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">5334019</t>
+          <t xml:space="preserve">5329943</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F22">
-        <v>1080</v>
+        <v>2581</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">311293989</t>
+          <t xml:space="preserve">311220566</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-23</t>
+          <t xml:space="preserve">2027-01-03</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1131,25 +1131,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">10196478</t>
+          <t xml:space="preserve">9065689, 100730166</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F23">
-        <v>760</v>
+        <v>8999</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">311490046</t>
+          <t xml:space="preserve">311221123</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-01-25</t>
+          <t xml:space="preserve">2027-01-05</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1181,25 +1181,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">5327777</t>
+          <t xml:space="preserve">5334019</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F24">
-        <v>1418</v>
+        <v>1080</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">311503382</t>
+          <t xml:space="preserve">311293989</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-15</t>
+          <t xml:space="preserve">2028-01-23</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1231,25 +1231,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">255560, 255561</t>
+          <t xml:space="preserve">10196478</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="F25">
-        <v>4613</v>
+        <v>760</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">311565109</t>
+          <t xml:space="preserve">311490046</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-30</t>
+          <t xml:space="preserve">2031-01-25</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1281,25 +1281,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">253097, 253098</t>
+          <t xml:space="preserve">5327777</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="F26">
-        <v>579</v>
+        <v>1418</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">311570567</t>
+          <t xml:space="preserve">311503382</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-04</t>
+          <t xml:space="preserve">2031-03-15</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1431,25 +1431,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">10196478</t>
+          <t xml:space="preserve">1352702</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F29">
-        <v>783</v>
+        <v>270</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">311795255</t>
+          <t xml:space="preserve">311769701</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-11-04</t>
+          <t xml:space="preserve">2034-06-27</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1481,25 +1481,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2277578</t>
+          <t xml:space="preserve">10196478</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="F30">
-        <v>576</v>
+        <v>783</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">311809061</t>
+          <t xml:space="preserve">311795255</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-01-31</t>
+          <t xml:space="preserve">2034-11-04</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1536,15 +1536,15 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="F31">
-        <v>1535</v>
+        <v>576</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">311809062</t>
+          <t xml:space="preserve">311809061</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1586,15 +1586,15 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F32">
-        <v>4410</v>
+        <v>1535</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">311809064</t>
+          <t xml:space="preserve">311809062</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1636,15 +1636,15 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F33">
-        <v>329</v>
+        <v>4410</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">311809060</t>
+          <t xml:space="preserve">311809064</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1681,20 +1681,20 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">5332677</t>
+          <t xml:space="preserve">2277578</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F34">
-        <v>812</v>
+        <v>329</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">311809074</t>
+          <t xml:space="preserve">311809060</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">7978652</t>
+          <t xml:space="preserve">5332677</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1740,11 +1740,11 @@
         </is>
       </c>
       <c r="F35">
-        <v>341</v>
+        <v>812</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">311809071</t>
+          <t xml:space="preserve">311809074</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1781,25 +1781,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">7978652</t>
+          <t xml:space="preserve">2288535</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F36">
-        <v>370</v>
+        <v>3002</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">311809071</t>
+          <t xml:space="preserve">311842620</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-01-31</t>
+          <t xml:space="preserve">2035-07-03</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -1831,25 +1831,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">7978652</t>
+          <t xml:space="preserve">2288535</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F37">
-        <v>278</v>
+        <v>1562</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">311809071</t>
+          <t xml:space="preserve">311842621</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-01-31</t>
+          <t xml:space="preserve">2035-07-03</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -1886,15 +1886,15 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F38">
-        <v>3002</v>
+        <v>738</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">311842620</t>
+          <t xml:space="preserve">311842624</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1936,11 +1936,11 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F39">
-        <v>1562</v>
+        <v>953</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1986,15 +1986,15 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F40">
-        <v>738</v>
+        <v>1125</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">311842624</t>
+          <t xml:space="preserve">311842621</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2036,11 +2036,11 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F41">
-        <v>953</v>
+        <v>567</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2086,11 +2086,11 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F42">
-        <v>1125</v>
+        <v>452</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2136,15 +2136,15 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F43">
-        <v>567</v>
+        <v>720</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">311842621</t>
+          <t xml:space="preserve">311842623</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2181,20 +2181,20 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2288535</t>
+          <t xml:space="preserve">2301907</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F44">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">311842621</t>
+          <t xml:space="preserve">311842619</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2231,25 +2231,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2288535</t>
+          <t xml:space="preserve">8113100</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F45">
-        <v>720</v>
+        <v>700</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">311842623</t>
+          <t xml:space="preserve">311845889</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-07-03</t>
+          <t xml:space="preserve">2035-07-23</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2301907</t>
+          <t xml:space="preserve">7978652</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2290,16 +2290,16 @@
         </is>
       </c>
       <c r="F46">
-        <v>447</v>
+        <v>341</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">311842619</t>
+          <t xml:space="preserve">311851736</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-07-03</t>
+          <t xml:space="preserve">2035-08-27</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2331,25 +2331,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">8113100</t>
+          <t xml:space="preserve">7978652</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F47">
-        <v>700</v>
+        <v>370</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">311845889</t>
+          <t xml:space="preserve">311851736</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-07-23</t>
+          <t xml:space="preserve">2035-08-27</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2381,25 +2381,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2281563</t>
+          <t xml:space="preserve">7978652</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F48">
-        <v>518</v>
+        <v>278</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">311853862</t>
+          <t xml:space="preserve">311851736</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-09-05</t>
+          <t xml:space="preserve">2035-08-27</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2325013</t>
+          <t xml:space="preserve">2281563</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2440,11 +2440,11 @@
         </is>
       </c>
       <c r="F49">
-        <v>444</v>
+        <v>518</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">311853869</t>
+          <t xml:space="preserve">311853862</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">5326332</t>
+          <t xml:space="preserve">2325013</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2490,11 +2490,11 @@
         </is>
       </c>
       <c r="F50">
-        <v>790</v>
+        <v>444</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">311853863</t>
+          <t xml:space="preserve">311853869</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">5329898</t>
+          <t xml:space="preserve">5326332</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2540,11 +2540,11 @@
         </is>
       </c>
       <c r="F51">
-        <v>265</v>
+        <v>790</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">311853870</t>
+          <t xml:space="preserve">311853863</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">7907154</t>
+          <t xml:space="preserve">5329898</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2590,11 +2590,11 @@
         </is>
       </c>
       <c r="F52">
-        <v>546</v>
+        <v>265</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">311853866</t>
+          <t xml:space="preserve">311853870</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">8265582</t>
+          <t xml:space="preserve">7907154</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2640,11 +2640,11 @@
         </is>
       </c>
       <c r="F53">
-        <v>611</v>
+        <v>546</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">311853867</t>
+          <t xml:space="preserve">311853866</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">5331000</t>
+          <t xml:space="preserve">8265582</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2690,16 +2690,16 @@
         </is>
       </c>
       <c r="F54">
-        <v>544</v>
+        <v>611</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">311854092</t>
+          <t xml:space="preserve">311853867</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-09-06</t>
+          <t xml:space="preserve">2035-09-05</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2731,20 +2731,20 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">5332000</t>
+          <t xml:space="preserve">5331000</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F55">
-        <v>1464</v>
+        <v>544</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311854090</t>
+          <t xml:space="preserve">311854092</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2781,20 +2781,20 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">9065689</t>
+          <t xml:space="preserve">5332000</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F56">
-        <v>2588</v>
+        <v>1464</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">311854089</t>
+          <t xml:space="preserve">311854090</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2836,15 +2836,15 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F57">
-        <v>1820</v>
+        <v>2588</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">311854091</t>
+          <t xml:space="preserve">311854089</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2886,15 +2886,15 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F58">
-        <v>4023</v>
+        <v>1820</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">311854093</t>
+          <t xml:space="preserve">311854091</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2931,25 +2931,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">10196478</t>
+          <t xml:space="preserve">9065689</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F59">
-        <v>702</v>
+        <v>4023</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">311858081</t>
+          <t xml:space="preserve">311854093</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-09-25</t>
+          <t xml:space="preserve">2035-09-06</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -2986,15 +2986,15 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F60">
-        <v>9576</v>
+        <v>702</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">311858083</t>
+          <t xml:space="preserve">311858081</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3031,20 +3031,20 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">5326640</t>
+          <t xml:space="preserve">10196478</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F61">
-        <v>2174</v>
+        <v>9576</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">311858071</t>
+          <t xml:space="preserve">311858083</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3086,11 +3086,11 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F62">
-        <v>1099</v>
+        <v>2174</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -3136,11 +3136,11 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F63">
-        <v>774</v>
+        <v>1099</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -3181,20 +3181,20 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">5329129</t>
+          <t xml:space="preserve">5326640</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F64">
-        <v>365</v>
+        <v>774</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311858079</t>
+          <t xml:space="preserve">311858071</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3231,7 +3231,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">7566192</t>
+          <t xml:space="preserve">5329129</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3240,11 +3240,11 @@
         </is>
       </c>
       <c r="F65">
-        <v>731</v>
+        <v>365</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311858077</t>
+          <t xml:space="preserve">311858079</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">7964466</t>
+          <t xml:space="preserve">7566192</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3290,11 +3290,11 @@
         </is>
       </c>
       <c r="F66">
-        <v>546</v>
+        <v>731</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311858076</t>
+          <t xml:space="preserve">311858077</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2254898</t>
+          <t xml:space="preserve">7964466</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3340,16 +3340,16 @@
         </is>
       </c>
       <c r="F67">
-        <v>303</v>
+        <v>546</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311858432</t>
+          <t xml:space="preserve">311858076</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-09-26</t>
+          <t xml:space="preserve">2035-09-25</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3381,7 +3381,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2254961</t>
+          <t xml:space="preserve">2254898</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3390,11 +3390,11 @@
         </is>
       </c>
       <c r="F68">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311858422</t>
+          <t xml:space="preserve">311858432</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">7004638</t>
+          <t xml:space="preserve">2254961</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -3440,11 +3440,11 @@
         </is>
       </c>
       <c r="F69">
-        <v>2940</v>
+        <v>299</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311858480</t>
+          <t xml:space="preserve">311858422</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3486,11 +3486,11 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F70">
-        <v>504</v>
+        <v>2940</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -3536,15 +3536,15 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F71">
-        <v>1404</v>
+        <v>504</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311858483</t>
+          <t xml:space="preserve">311858480</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3586,15 +3586,15 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F72">
-        <v>652</v>
+        <v>1404</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311858480</t>
+          <t xml:space="preserve">311858483</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3631,25 +3631,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">5327777</t>
+          <t xml:space="preserve">7004638</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F73">
-        <v>6103</v>
+        <v>652</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311861223</t>
+          <t xml:space="preserve">311858480</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-10</t>
+          <t xml:space="preserve">2035-09-26</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3686,15 +3686,15 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F74">
-        <v>480</v>
+        <v>6103</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311861225</t>
+          <t xml:space="preserve">311861223</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3736,15 +3736,15 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F75">
-        <v>374</v>
+        <v>480</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311861224</t>
+          <t xml:space="preserve">311861225</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3781,20 +3781,20 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">9633243</t>
+          <t xml:space="preserve">5327777</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F76">
-        <v>495</v>
+        <v>374</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311861196</t>
+          <t xml:space="preserve">311861224</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -3836,11 +3836,11 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F77">
-        <v>565</v>
+        <v>495</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -3881,25 +3881,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2301632</t>
+          <t xml:space="preserve">9633243</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F78">
-        <v>288</v>
+        <v>565</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311862715</t>
+          <t xml:space="preserve">311861196</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-17</t>
+          <t xml:space="preserve">2035-10-10</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -3931,20 +3931,20 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">5328892</t>
+          <t xml:space="preserve">2301632</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F79">
-        <v>469</v>
+        <v>288</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311862707</t>
+          <t xml:space="preserve">311862715</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3986,11 +3986,11 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F80">
-        <v>367</v>
+        <v>469</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -4036,11 +4036,11 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="F81">
-        <v>347</v>
+        <v>367</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -4086,15 +4086,15 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="F82">
-        <v>609</v>
+        <v>347</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311862706</t>
+          <t xml:space="preserve">311862707</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4136,11 +4136,11 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F83">
-        <v>694</v>
+        <v>609</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -4181,20 +4181,20 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">7690922</t>
+          <t xml:space="preserve">5328892</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F84">
-        <v>461</v>
+        <v>694</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311862710</t>
+          <t xml:space="preserve">311862706</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">9065626</t>
+          <t xml:space="preserve">7690922</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -4240,11 +4240,11 @@
         </is>
       </c>
       <c r="F85">
-        <v>385</v>
+        <v>461</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311862716</t>
+          <t xml:space="preserve">311862710</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4286,20 +4286,20 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F86">
-        <v>496</v>
+        <v>385</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311865617</t>
+          <t xml:space="preserve">311862716</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-31</t>
+          <t xml:space="preserve">2035-10-17</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -4331,20 +4331,20 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">9712207</t>
+          <t xml:space="preserve">9065626</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F87">
-        <v>995</v>
+        <v>496</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311865616</t>
+          <t xml:space="preserve">311865617</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">5330857</t>
+          <t xml:space="preserve">9712207</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -4390,16 +4390,16 @@
         </is>
       </c>
       <c r="F88">
-        <v>571</v>
+        <v>995</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311871335</t>
+          <t xml:space="preserve">311865616</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-02</t>
+          <t xml:space="preserve">2035-10-31</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">5330869</t>
+          <t xml:space="preserve">5330857</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -4440,11 +4440,11 @@
         </is>
       </c>
       <c r="F89">
-        <v>435</v>
+        <v>571</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311871336</t>
+          <t xml:space="preserve">311871335</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -4481,25 +4481,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">1352718</t>
+          <t xml:space="preserve">5330869</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F90">
-        <v>734</v>
+        <v>435</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311871441</t>
+          <t xml:space="preserve">311871336</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-03</t>
+          <t xml:space="preserve">2035-12-02</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -4531,20 +4531,20 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2246519</t>
+          <t xml:space="preserve">1352718</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F91">
-        <v>322</v>
+        <v>734</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311871450</t>
+          <t xml:space="preserve">311871441</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2301964</t>
+          <t xml:space="preserve">2246519</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -4590,11 +4590,11 @@
         </is>
       </c>
       <c r="F92">
-        <v>537</v>
+        <v>322</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311871491</t>
+          <t xml:space="preserve">311871450</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4631,20 +4631,20 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">5326967</t>
+          <t xml:space="preserve">2301964</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F93">
-        <v>616</v>
+        <v>537</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311871599</t>
+          <t xml:space="preserve">311871491</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -4681,20 +4681,20 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">5326982</t>
+          <t xml:space="preserve">5326967</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F94">
-        <v>403</v>
+        <v>616</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311871598</t>
+          <t xml:space="preserve">311871599</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">5330557</t>
+          <t xml:space="preserve">5326982</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -4740,11 +4740,11 @@
         </is>
       </c>
       <c r="F95">
-        <v>331</v>
+        <v>403</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311871490</t>
+          <t xml:space="preserve">311871598</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4786,11 +4786,11 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F96">
-        <v>258</v>
+        <v>331</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -4831,20 +4831,20 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">9065569</t>
+          <t xml:space="preserve">5330557</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F97">
-        <v>310</v>
+        <v>258</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311871489</t>
+          <t xml:space="preserve">311871490</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">9595470</t>
+          <t xml:space="preserve">9065569</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -4890,11 +4890,11 @@
         </is>
       </c>
       <c r="F98">
-        <v>664</v>
+        <v>310</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311871451</t>
+          <t xml:space="preserve">311871487</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -4931,20 +4931,20 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">9924661</t>
+          <t xml:space="preserve">9595470</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F99">
-        <v>535</v>
+        <v>664</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311871443</t>
+          <t xml:space="preserve">311871451</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -4986,11 +4986,11 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F100">
-        <v>450</v>
+        <v>535</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -5036,11 +5036,11 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F101">
-        <v>795</v>
+        <v>450</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -5086,11 +5086,11 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F102">
-        <v>409</v>
+        <v>795</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -5136,11 +5136,11 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="F103">
-        <v>1473</v>
+        <v>409</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -5186,11 +5186,11 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F104">
-        <v>587</v>
+        <v>1473</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -5236,11 +5236,11 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F105">
-        <v>1379</v>
+        <v>587</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -5286,11 +5286,11 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F106">
-        <v>320</v>
+        <v>1379</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -5331,25 +5331,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2246414</t>
+          <t xml:space="preserve">9924661</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F107">
-        <v>609</v>
+        <v>320</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311871859</t>
+          <t xml:space="preserve">311871443</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-04</t>
+          <t xml:space="preserve">2035-12-03</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2324233</t>
+          <t xml:space="preserve">2246414</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -5390,11 +5390,11 @@
         </is>
       </c>
       <c r="F108">
-        <v>412</v>
+        <v>609</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311871863</t>
+          <t xml:space="preserve">311871859</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2254877</t>
+          <t xml:space="preserve">2324233</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -5440,16 +5440,16 @@
         </is>
       </c>
       <c r="F109">
-        <v>490</v>
+        <v>412</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311872069</t>
+          <t xml:space="preserve">311871863</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-05</t>
+          <t xml:space="preserve">2035-12-04</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -5486,15 +5486,15 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F110">
-        <v>1466</v>
+        <v>490</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311872068</t>
+          <t xml:space="preserve">311872069</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -5531,25 +5531,25 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">7568565</t>
+          <t xml:space="preserve">2254877</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F111">
-        <v>1448</v>
+        <v>1466</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311872207</t>
+          <t xml:space="preserve">311872068</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-08</t>
+          <t xml:space="preserve">2035-12-05</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -5581,7 +5581,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">1352718</t>
+          <t xml:space="preserve">7568565</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -5590,16 +5590,16 @@
         </is>
       </c>
       <c r="F112">
-        <v>934</v>
+        <v>1448</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311872602</t>
+          <t xml:space="preserve">311872207</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-09</t>
+          <t xml:space="preserve">2035-12-08</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -5636,11 +5636,11 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F113">
-        <v>840</v>
+        <v>934</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -5686,11 +5686,11 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F114">
-        <v>1427</v>
+        <v>840</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -5736,11 +5736,11 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F115">
-        <v>934</v>
+        <v>1427</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -5786,11 +5786,11 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F116">
-        <v>1868</v>
+        <v>934</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -5836,11 +5836,11 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F117">
-        <v>1894</v>
+        <v>1868</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -5886,11 +5886,11 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F118">
-        <v>3578</v>
+        <v>1894</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -5936,11 +5936,11 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F119">
-        <v>1868</v>
+        <v>3578</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
@@ -5981,20 +5981,20 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2281030</t>
+          <t xml:space="preserve">1352718</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F120">
-        <v>394</v>
+        <v>1868</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311872484</t>
+          <t xml:space="preserve">311872602</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2301858</t>
+          <t xml:space="preserve">2281030</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -6040,11 +6040,11 @@
         </is>
       </c>
       <c r="F121">
-        <v>6286</v>
+        <v>394</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311872502</t>
+          <t xml:space="preserve">311872484</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -6086,11 +6086,11 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F122">
-        <v>1330</v>
+        <v>6286</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
@@ -6136,11 +6136,11 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F123">
-        <v>1325</v>
+        <v>1330</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
@@ -6186,11 +6186,11 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F124">
-        <v>1647</v>
+        <v>1325</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
@@ -6236,11 +6236,11 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F125">
-        <v>2474</v>
+        <v>1647</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
@@ -6286,11 +6286,11 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F126">
-        <v>387</v>
+        <v>2474</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
@@ -6331,20 +6331,20 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">5328179</t>
+          <t xml:space="preserve">2301858</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F127">
-        <v>575</v>
+        <v>387</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311872485</t>
+          <t xml:space="preserve">311872502</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -6381,20 +6381,20 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">5328262, 100655352</t>
+          <t xml:space="preserve">5328179</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F128">
-        <v>480</v>
+        <v>575</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311872503</t>
+          <t xml:space="preserve">311872485</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -6431,7 +6431,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">5329897</t>
+          <t xml:space="preserve">5328262, 100655352</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -6440,11 +6440,11 @@
         </is>
       </c>
       <c r="F129">
-        <v>428</v>
+        <v>480</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311872481</t>
+          <t xml:space="preserve">311872503</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -6486,15 +6486,15 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F130">
-        <v>380</v>
+        <v>428</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311872482</t>
+          <t xml:space="preserve">311872481</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -6531,25 +6531,25 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t xml:space="preserve">5331670</t>
+          <t xml:space="preserve">5329897</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F131">
-        <v>3098</v>
+        <v>380</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311873647</t>
+          <t xml:space="preserve">311872482</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-16</t>
+          <t xml:space="preserve">2035-12-09</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -6586,11 +6586,11 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F132">
-        <v>1957</v>
+        <v>3098</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
@@ -6636,11 +6636,11 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F133">
-        <v>4724</v>
+        <v>1957</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
@@ -6686,11 +6686,11 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F134">
-        <v>963</v>
+        <v>4724</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
@@ -6736,11 +6736,11 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F135">
-        <v>1827</v>
+        <v>963</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
@@ -6786,11 +6786,11 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F136">
-        <v>2279</v>
+        <v>1827</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
@@ -6831,25 +6831,25 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t xml:space="preserve">1307795</t>
+          <t xml:space="preserve">5331670</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F137">
-        <v>278</v>
+        <v>2279</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874086</t>
+          <t xml:space="preserve">311873647</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-17</t>
+          <t xml:space="preserve">2035-12-16</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -6881,7 +6881,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2254667</t>
+          <t xml:space="preserve">1307795</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -6890,11 +6890,11 @@
         </is>
       </c>
       <c r="F138">
-        <v>359</v>
+        <v>278</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874085</t>
+          <t xml:space="preserve">311874086</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -6931,7 +6931,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2278059</t>
+          <t xml:space="preserve">2254667</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -6940,11 +6940,11 @@
         </is>
       </c>
       <c r="F139">
-        <v>395</v>
+        <v>359</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874093</t>
+          <t xml:space="preserve">311874085</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -6981,7 +6981,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t xml:space="preserve">5326860</t>
+          <t xml:space="preserve">2278059</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -6990,11 +6990,11 @@
         </is>
       </c>
       <c r="F140">
-        <v>635</v>
+        <v>395</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874090</t>
+          <t xml:space="preserve">311874093</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -7036,11 +7036,11 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F141">
-        <v>288</v>
+        <v>635</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
@@ -7086,11 +7086,11 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F142">
-        <v>1214</v>
+        <v>288</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
@@ -7136,15 +7136,15 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F143">
-        <v>1535</v>
+        <v>1214</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874091</t>
+          <t xml:space="preserve">311874090</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -7181,20 +7181,20 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t xml:space="preserve">5327773</t>
+          <t xml:space="preserve">5326860</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F144">
-        <v>1459</v>
+        <v>1535</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874087</t>
+          <t xml:space="preserve">311874091</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -7236,11 +7236,11 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F145">
-        <v>744</v>
+        <v>1459</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
@@ -7281,20 +7281,20 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t xml:space="preserve">5333179</t>
+          <t xml:space="preserve">5327773</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F146">
-        <v>659</v>
+        <v>744</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874088</t>
+          <t xml:space="preserve">311874087</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -7331,20 +7331,20 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t xml:space="preserve">7416190</t>
+          <t xml:space="preserve">5333179</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F147">
-        <v>2227</v>
+        <v>659</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874092</t>
+          <t xml:space="preserve">311874088</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -7381,20 +7381,20 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t xml:space="preserve">9725751</t>
+          <t xml:space="preserve">7416190</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F148">
-        <v>760</v>
+        <v>2227</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874089</t>
+          <t xml:space="preserve">311874092</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -7431,7 +7431,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t xml:space="preserve">10026444</t>
+          <t xml:space="preserve">9725751</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -7440,16 +7440,16 @@
         </is>
       </c>
       <c r="F149">
-        <v>864</v>
+        <v>760</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874136</t>
+          <t xml:space="preserve">311874089</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-18</t>
+          <t xml:space="preserve">2035-12-17</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -7481,7 +7481,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">5326298</t>
+          <t xml:space="preserve">10026444</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -7490,11 +7490,11 @@
         </is>
       </c>
       <c r="F150">
-        <v>261</v>
+        <v>864</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874135</t>
+          <t xml:space="preserve">311874136</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t xml:space="preserve">5328508</t>
+          <t xml:space="preserve">5326298</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -7540,11 +7540,11 @@
         </is>
       </c>
       <c r="F151">
-        <v>874</v>
+        <v>261</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874134</t>
+          <t xml:space="preserve">311874135</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -7581,7 +7581,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t xml:space="preserve">5328509</t>
+          <t xml:space="preserve">5328508</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -7590,11 +7590,11 @@
         </is>
       </c>
       <c r="F152">
-        <v>931</v>
+        <v>874</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874133</t>
+          <t xml:space="preserve">311874134</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t xml:space="preserve">7004602</t>
+          <t xml:space="preserve">5328509</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -7640,11 +7640,11 @@
         </is>
       </c>
       <c r="F153">
-        <v>1119</v>
+        <v>931</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874138</t>
+          <t xml:space="preserve">311874133</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -7686,11 +7686,11 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F154">
-        <v>570</v>
+        <v>1119</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
@@ -7736,11 +7736,11 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F155">
-        <v>456</v>
+        <v>570</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
@@ -7781,20 +7781,20 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t xml:space="preserve">7629375</t>
+          <t xml:space="preserve">7004602</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F156">
-        <v>735</v>
+        <v>456</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874137</t>
+          <t xml:space="preserve">311874138</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -7836,11 +7836,11 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F157">
-        <v>310</v>
+        <v>735</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
@@ -7881,20 +7881,20 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t xml:space="preserve">9065650</t>
+          <t xml:space="preserve">7629375</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F158">
-        <v>366</v>
+        <v>310</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874139</t>
+          <t xml:space="preserve">311874137</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -7931,7 +7931,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2301750</t>
+          <t xml:space="preserve">9065650</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -7940,16 +7940,16 @@
         </is>
       </c>
       <c r="F159">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874648</t>
+          <t xml:space="preserve">311874139</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-19</t>
+          <t xml:space="preserve">2035-12-18</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -7981,7 +7981,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2325409</t>
+          <t xml:space="preserve">2301750</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -7990,11 +7990,11 @@
         </is>
       </c>
       <c r="F160">
-        <v>334</v>
+        <v>356</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874645</t>
+          <t xml:space="preserve">311874648</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t xml:space="preserve">5329171</t>
+          <t xml:space="preserve">2325409</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -8040,11 +8040,11 @@
         </is>
       </c>
       <c r="F161">
-        <v>257</v>
+        <v>334</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874644</t>
+          <t xml:space="preserve">311874645</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t xml:space="preserve">5330379</t>
+          <t xml:space="preserve">5329171</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -8090,11 +8090,11 @@
         </is>
       </c>
       <c r="F162">
-        <v>458</v>
+        <v>257</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874647</t>
+          <t xml:space="preserve">311874644</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -8131,20 +8131,20 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t xml:space="preserve">5333853</t>
+          <t xml:space="preserve">5330379</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F163">
-        <v>1392</v>
+        <v>458</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874646</t>
+          <t xml:space="preserve">311874647</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -8181,25 +8181,25 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t xml:space="preserve">1352822</t>
+          <t xml:space="preserve">5333853</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F164">
-        <v>360</v>
+        <v>1392</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875283</t>
+          <t xml:space="preserve">311874646</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-01-06</t>
+          <t xml:space="preserve">2035-12-19</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -8231,20 +8231,20 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t xml:space="preserve">5327108</t>
+          <t xml:space="preserve">1352822</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F165">
-        <v>847</v>
+        <v>360</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875278</t>
+          <t xml:space="preserve">311875283</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -8286,11 +8286,11 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F166">
-        <v>640</v>
+        <v>847</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
@@ -8331,20 +8331,20 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t xml:space="preserve">5328529</t>
+          <t xml:space="preserve">5327108</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F167">
-        <v>5038</v>
+        <v>640</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875280</t>
+          <t xml:space="preserve">311875278</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -8381,7 +8381,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t xml:space="preserve">10130052</t>
+          <t xml:space="preserve">5328529</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -8390,16 +8390,16 @@
         </is>
       </c>
       <c r="F168">
-        <v>1306</v>
+        <v>5038</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875473</t>
+          <t xml:space="preserve">311875280</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-01-07</t>
+          <t xml:space="preserve">2036-01-06</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2246500</t>
+          <t xml:space="preserve">10130052</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -8440,11 +8440,11 @@
         </is>
       </c>
       <c r="F169">
-        <v>585</v>
+        <v>1306</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875477</t>
+          <t xml:space="preserve">311875473</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -8486,11 +8486,11 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F170">
-        <v>1205</v>
+        <v>585</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
@@ -8536,11 +8536,11 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F171">
-        <v>272</v>
+        <v>1205</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
@@ -8581,20 +8581,20 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2261352</t>
+          <t xml:space="preserve">2246500</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F172">
-        <v>956</v>
+        <v>272</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875478</t>
+          <t xml:space="preserve">311875477</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -8636,11 +8636,11 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F173">
-        <v>1059</v>
+        <v>956</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
@@ -8681,20 +8681,20 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t xml:space="preserve">5326297</t>
+          <t xml:space="preserve">2261352</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F174">
-        <v>431</v>
+        <v>1059</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875479</t>
+          <t xml:space="preserve">311875478</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -8731,7 +8731,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t xml:space="preserve">5327094</t>
+          <t xml:space="preserve">5326297</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -8740,11 +8740,11 @@
         </is>
       </c>
       <c r="F175">
-        <v>283</v>
+        <v>431</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875481</t>
+          <t xml:space="preserve">311875479</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -8781,20 +8781,20 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t xml:space="preserve">5333967</t>
+          <t xml:space="preserve">5327094</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F176">
-        <v>1670</v>
+        <v>283</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875474</t>
+          <t xml:space="preserve">311875481</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -8836,15 +8836,15 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F177">
-        <v>1318</v>
+        <v>1670</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875475</t>
+          <t xml:space="preserve">311875474</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -8881,20 +8881,20 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t xml:space="preserve">7004605</t>
+          <t xml:space="preserve">5333967</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F178">
-        <v>5933</v>
+        <v>1318</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875476</t>
+          <t xml:space="preserve">311875475</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -8931,7 +8931,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t xml:space="preserve">5330767</t>
+          <t xml:space="preserve">7004605</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -8940,16 +8940,16 @@
         </is>
       </c>
       <c r="F179">
-        <v>360</v>
+        <v>5933</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311879987</t>
+          <t xml:space="preserve">311875476</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-02-02</t>
+          <t xml:space="preserve">2036-01-07</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -8981,7 +8981,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t xml:space="preserve">9065587</t>
+          <t xml:space="preserve">5330767</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -8990,11 +8990,11 @@
         </is>
       </c>
       <c r="F180">
-        <v>987</v>
+        <v>360</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311879989</t>
+          <t xml:space="preserve">311879987</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -9036,11 +9036,11 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F181">
-        <v>1764</v>
+        <v>987</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
@@ -9086,11 +9086,11 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F182">
-        <v>2249</v>
+        <v>1764</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
@@ -9136,15 +9136,15 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="F183">
-        <v>1768</v>
+        <v>2249</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311879988</t>
+          <t xml:space="preserve">311879989</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -9186,15 +9186,15 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="F184">
-        <v>441</v>
+        <v>1768</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311879989</t>
+          <t xml:space="preserve">311879988</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -9236,11 +9236,11 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F185">
-        <v>3090</v>
+        <v>441</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
@@ -9281,25 +9281,25 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t xml:space="preserve">5330163</t>
+          <t xml:space="preserve">9065587</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F186">
-        <v>554</v>
+        <v>3090</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311880018</t>
+          <t xml:space="preserve">311879989</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-02-03</t>
+          <t xml:space="preserve">2036-02-02</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -9331,7 +9331,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2254669</t>
+          <t xml:space="preserve">5330163</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -9340,16 +9340,16 @@
         </is>
       </c>
       <c r="F187">
-        <v>421</v>
+        <v>554</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311880347</t>
+          <t xml:space="preserve">311880018</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-02-04</t>
+          <t xml:space="preserve">2036-02-03</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -9381,7 +9381,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t xml:space="preserve">2261587</t>
+          <t xml:space="preserve">2254669</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -9390,11 +9390,11 @@
         </is>
       </c>
       <c r="F188">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311880341</t>
+          <t xml:space="preserve">311880347</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -9431,7 +9431,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t xml:space="preserve">2261594</t>
+          <t xml:space="preserve">2261587</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -9440,11 +9440,11 @@
         </is>
       </c>
       <c r="F189">
-        <v>464</v>
+        <v>424</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311880338</t>
+          <t xml:space="preserve">311880341</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -9481,7 +9481,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t xml:space="preserve">2289366</t>
+          <t xml:space="preserve">2261594</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -9490,11 +9490,11 @@
         </is>
       </c>
       <c r="F190">
-        <v>743</v>
+        <v>464</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t xml:space="preserve">311880350</t>
+          <t xml:space="preserve">311880338</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -9531,7 +9531,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t xml:space="preserve">2301595</t>
+          <t xml:space="preserve">2289366</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -9540,11 +9540,11 @@
         </is>
       </c>
       <c r="F191">
-        <v>437</v>
+        <v>743</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t xml:space="preserve">311880344</t>
+          <t xml:space="preserve">311880350</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t xml:space="preserve">257561</t>
+          <t xml:space="preserve">2301595</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -9590,11 +9590,11 @@
         </is>
       </c>
       <c r="F192">
-        <v>1949</v>
+        <v>437</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t xml:space="preserve">311880345</t>
+          <t xml:space="preserve">311880344</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">

--- a/public/exports/29189366.xlsx
+++ b/public/exports/29189366.xlsx
@@ -91,26 +91,26 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kaj Sommers Vej 29</t>
+          <t xml:space="preserve">Carlsbergvej 13</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3320</t>
+          <t xml:space="preserve">3400</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10026444</t>
+          <t xml:space="preserve">5327777</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="H2">
-        <v>600</v>
+        <v>2217</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -151,17 +151,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hulvejen 31</t>
+          <t xml:space="preserve">Gørløsevej 6A</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3400</t>
+          <t xml:space="preserve">3550</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100795387</t>
+          <t xml:space="preserve">717932, 2261588</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -170,7 +170,7 @@
         </is>
       </c>
       <c r="H3">
-        <v>465</v>
+        <v>2285</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -211,17 +211,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nødebovej 38E</t>
+          <t xml:space="preserve">Hulvejen 31</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3480</t>
+          <t xml:space="preserve">3400</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">253097, 253098</t>
+          <t xml:space="preserve">100795387</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -230,7 +230,7 @@
         </is>
       </c>
       <c r="H4">
-        <v>579</v>
+        <v>465</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -271,7 +271,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skansevej 2D</t>
+          <t xml:space="preserve">Jespervej 146B</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -281,16 +281,16 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">255560, 255561</t>
+          <t xml:space="preserve">5329943</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="H5">
-        <v>4613</v>
+        <v>270</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -331,7 +331,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordstensvej 1</t>
+          <t xml:space="preserve">Jespervej 148</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -341,16 +341,16 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">257561</t>
+          <t xml:space="preserve">5329943</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H6">
-        <v>1949</v>
+        <v>427</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -391,7 +391,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carlsbergvej 13</t>
+          <t xml:space="preserve">Jespervej 148</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -401,16 +401,16 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">5327777</t>
+          <t xml:space="preserve">5329943</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H7">
-        <v>2217</v>
+        <v>553</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -451,7 +451,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Milnersvej 35F</t>
+          <t xml:space="preserve">Jespervej 148</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -461,16 +461,16 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">5328529, 100965431</t>
+          <t xml:space="preserve">5329943</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="H8">
-        <v>1368</v>
+        <v>553</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -526,11 +526,11 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="H9">
-        <v>427</v>
+        <v>553</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -586,11 +586,11 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="H10">
-        <v>553</v>
+        <v>427</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -646,11 +646,11 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H11">
-        <v>553</v>
+        <v>2384</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -706,11 +706,11 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H12">
-        <v>553</v>
+        <v>1056</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -766,11 +766,11 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H13">
-        <v>427</v>
+        <v>989</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -826,11 +826,11 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H14">
-        <v>2384</v>
+        <v>989</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jespervej 146B</t>
+          <t xml:space="preserve">Jespervej 148</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -886,11 +886,11 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H15">
-        <v>270</v>
+        <v>989</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -931,17 +931,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jespervej 148</t>
+          <t xml:space="preserve">Kaj Sommers Vej 29</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">3400</t>
+          <t xml:space="preserve">3320</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">5329943</t>
+          <t xml:space="preserve">10026444</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="H16">
-        <v>1056</v>
+        <v>600</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jespervej 148</t>
+          <t xml:space="preserve">Milnersvej 35F</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1001,16 +1001,16 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">5329943</t>
+          <t xml:space="preserve">5328529, 100965431</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H17">
-        <v>989</v>
+        <v>1368</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jespervej 148</t>
+          <t xml:space="preserve">Milnersvej 39A</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1061,30 +1061,30 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">5329943</t>
+          <t xml:space="preserve">717923, 10036947</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H18">
-        <v>989</v>
+        <v>8327</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200056514</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2022-01-08</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jespervej 148</t>
+          <t xml:space="preserve">Jespervej 152</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1126,30 +1126,30 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H19">
-        <v>989</v>
+        <v>2581</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311220566</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2027-01-03</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -1171,45 +1171,45 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gørløsevej 6A</t>
+          <t xml:space="preserve">Milnersvej 39C</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">3550</t>
+          <t xml:space="preserve">3400</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">717932, 2261588</t>
+          <t xml:space="preserve">9065689, 100730166</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="H20">
-        <v>2285</v>
+        <v>8999</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311221123</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2027-01-05</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Milnersvej 39A</t>
+          <t xml:space="preserve">Ægirsvej 4</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1241,35 +1241,35 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">717923, 10036947</t>
+          <t xml:space="preserve">5334019</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H21">
-        <v>8327</v>
+        <v>1080</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">200056514</t>
+          <t xml:space="preserve">311293989</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-01-08</t>
+          <t xml:space="preserve">2028-01-23</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jespervej 152</t>
+          <t xml:space="preserve">Roskildevej 18</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1301,25 +1301,25 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">5329943</t>
+          <t xml:space="preserve">10196478</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="H22">
-        <v>2581</v>
+        <v>760</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">311220566</t>
+          <t xml:space="preserve">311490046</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-03</t>
+          <t xml:space="preserve">2031-01-25</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Milnersvej 39C</t>
+          <t xml:space="preserve">Carlsbergvej 13B</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1361,25 +1361,25 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">9065689, 100730166</t>
+          <t xml:space="preserve">5327777</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="H23">
-        <v>8999</v>
+        <v>1418</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t xml:space="preserve">311221123</t>
+          <t xml:space="preserve">311503382</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-05</t>
+          <t xml:space="preserve">2031-03-15</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ægirsvej 4</t>
+          <t xml:space="preserve">Skansevej 2D</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">5334019</t>
+          <t xml:space="preserve">255560, 255561</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1430,16 +1430,16 @@
         </is>
       </c>
       <c r="H24">
-        <v>1080</v>
+        <v>4613</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">311293989</t>
+          <t xml:space="preserve">311565109</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-23</t>
+          <t xml:space="preserve">2031-11-30</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1471,35 +1471,35 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Roskildevej 18</t>
+          <t xml:space="preserve">Nødebovej 38E</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">3400</t>
+          <t xml:space="preserve">3480</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">10196478</t>
+          <t xml:space="preserve">253097, 253098</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H25">
-        <v>760</v>
+        <v>579</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">311490046</t>
+          <t xml:space="preserve">311570567</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-01-25</t>
+          <t xml:space="preserve">2032-01-04</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carlsbergvej 13B</t>
+          <t xml:space="preserve">Roskildevej 16</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1541,25 +1541,25 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">5327777</t>
+          <t xml:space="preserve">100000562</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H26">
-        <v>1418</v>
+        <v>1733</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">311503382</t>
+          <t xml:space="preserve">311604055</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-15</t>
+          <t xml:space="preserve">2032-05-30</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -1591,7 +1591,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Roskildevej 16</t>
+          <t xml:space="preserve">Buevej 1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1601,25 +1601,25 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">100000562</t>
+          <t xml:space="preserve">1352702</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H27">
-        <v>1733</v>
+        <v>270</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">311604055</t>
+          <t xml:space="preserve">311769701</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-30</t>
+          <t xml:space="preserve">2034-06-27</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buevej 1</t>
+          <t xml:space="preserve">Roskildevej 18</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1721,25 +1721,25 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">1352702</t>
+          <t xml:space="preserve">10196478</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="H29">
-        <v>270</v>
+        <v>783</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">311769701</t>
+          <t xml:space="preserve">311795255</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-06-27</t>
+          <t xml:space="preserve">2034-11-04</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Roskildevej 18</t>
+          <t xml:space="preserve">Baunevej 10</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1781,25 +1781,25 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">10196478</t>
+          <t xml:space="preserve">2277578</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H30">
-        <v>783</v>
+        <v>4410</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">311795255</t>
+          <t xml:space="preserve">311809064</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-11-04</t>
+          <t xml:space="preserve">2035-01-31</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baunevej 12</t>
+          <t xml:space="preserve">Baunevej 10</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1846,15 +1846,15 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H31">
-        <v>576</v>
+        <v>329</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">311809066</t>
+          <t xml:space="preserve">311809060</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baunevej 8</t>
+          <t xml:space="preserve">Baunevej 12</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1906,15 +1906,15 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="H32">
-        <v>1535</v>
+        <v>576</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">311809062</t>
+          <t xml:space="preserve">311809061</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baunevej 10</t>
+          <t xml:space="preserve">Baunevej 8</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1966,15 +1966,15 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H33">
-        <v>4410</v>
+        <v>1535</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">311809066</t>
+          <t xml:space="preserve">311809062</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baunevej 10</t>
+          <t xml:space="preserve">Thurahsvej 4</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2021,20 +2021,20 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2277578</t>
+          <t xml:space="preserve">5332677</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H34">
-        <v>329</v>
+        <v>812</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">311809066</t>
+          <t xml:space="preserve">311809074</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2071,17 +2071,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thurahsvej 4</t>
+          <t xml:space="preserve">Ny Harløsevej 15A</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">3400</t>
+          <t xml:space="preserve">3320</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">5332677</t>
+          <t xml:space="preserve">2288535</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2090,16 +2090,16 @@
         </is>
       </c>
       <c r="H35">
-        <v>812</v>
+        <v>3002</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">311809074</t>
+          <t xml:space="preserve">311842620</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-01-31</t>
+          <t xml:space="preserve">2035-07-03</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ny Harløsevej 15A</t>
+          <t xml:space="preserve">Ny Harløsevej 17</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2146,15 +2146,15 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H36">
-        <v>3002</v>
+        <v>1562</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">311842620</t>
+          <t xml:space="preserve">311842621</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2206,11 +2206,11 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H37">
-        <v>1562</v>
+        <v>953</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ny Harløsevej 17K</t>
+          <t xml:space="preserve">Ny Harløsevej 17</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2266,15 +2266,15 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H38">
-        <v>738</v>
+        <v>1125</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">311842624</t>
+          <t xml:space="preserve">311842621</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2326,11 +2326,11 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H39">
-        <v>953</v>
+        <v>567</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2386,11 +2386,11 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H40">
-        <v>1125</v>
+        <v>452</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ny Harløsevej 17</t>
+          <t xml:space="preserve">Ny Harløsevej 17F</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2446,15 +2446,15 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H41">
-        <v>567</v>
+        <v>720</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">311842621</t>
+          <t xml:space="preserve">311842623</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ny Harløsevej 17</t>
+          <t xml:space="preserve">Ny Harløsevej 17K</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2506,15 +2506,15 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="H42">
-        <v>452</v>
+        <v>738</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">311842621</t>
+          <t xml:space="preserve">311842624</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2551,30 +2551,30 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ny Harløsevej 17F</t>
+          <t xml:space="preserve">Ålholmparken 2</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">3320</t>
+          <t xml:space="preserve">3400</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2288535</t>
+          <t xml:space="preserve">2301907</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H43">
-        <v>720</v>
+        <v>447</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">311842623</t>
+          <t xml:space="preserve">311842619</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ålholmparken 2</t>
+          <t xml:space="preserve">Rankeskovvej 6</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2621,25 +2621,25 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2301907</t>
+          <t xml:space="preserve">8113100</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H44">
-        <v>447</v>
+        <v>700</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">311842619</t>
+          <t xml:space="preserve">311845889</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-07-03</t>
+          <t xml:space="preserve">2035-07-23</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -2671,35 +2671,35 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rankeskovvej 6</t>
+          <t xml:space="preserve">Skolevej 2</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">3400</t>
+          <t xml:space="preserve">3480</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">8113100</t>
+          <t xml:space="preserve">7978652</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H45">
-        <v>700</v>
+        <v>341</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">311845889</t>
+          <t xml:space="preserve">311851736</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-07-23</t>
+          <t xml:space="preserve">2035-08-27</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -2746,11 +2746,11 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H46">
-        <v>341</v>
+        <v>370</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2806,11 +2806,11 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H47">
-        <v>370</v>
+        <v>278</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2851,35 +2851,35 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 2</t>
+          <t xml:space="preserve">Bremerholmen 21</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">3480</t>
+          <t xml:space="preserve">3320</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">7978652</t>
+          <t xml:space="preserve">2281563</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H48">
-        <v>278</v>
+        <v>518</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">311851736</t>
+          <t xml:space="preserve">311853862</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-08-27</t>
+          <t xml:space="preserve">2035-09-05</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -2911,17 +2911,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bremerholmen 21</t>
+          <t xml:space="preserve">Clausensvej 4</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">3320</t>
+          <t xml:space="preserve">3400</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2281563</t>
+          <t xml:space="preserve">5329898</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2930,11 +2930,11 @@
         </is>
       </c>
       <c r="H49">
-        <v>518</v>
+        <v>265</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">311853862</t>
+          <t xml:space="preserve">311853870</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -2971,17 +2971,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirstinehøj 17</t>
+          <t xml:space="preserve">Elver Alle 2</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">3480</t>
+          <t xml:space="preserve">3400</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2325013</t>
+          <t xml:space="preserve">7907154</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2990,11 +2990,11 @@
         </is>
       </c>
       <c r="H50">
-        <v>444</v>
+        <v>546</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">311853869</t>
+          <t xml:space="preserve">311853866</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllestræde 18</t>
+          <t xml:space="preserve">Elver Alle 4</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">5326332</t>
+          <t xml:space="preserve">8265582</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3050,11 +3050,11 @@
         </is>
       </c>
       <c r="H51">
-        <v>790</v>
+        <v>611</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">311853863</t>
+          <t xml:space="preserve">311853867</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3091,17 +3091,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Clausensvej 4</t>
+          <t xml:space="preserve">Kirstinehøj 17</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">3400</t>
+          <t xml:space="preserve">3480</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">5329898</t>
+          <t xml:space="preserve">2325013</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3110,11 +3110,11 @@
         </is>
       </c>
       <c r="H52">
-        <v>265</v>
+        <v>444</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">311853870</t>
+          <t xml:space="preserve">311853869</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elver Alle 2</t>
+          <t xml:space="preserve">Møllestræde 18</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">7907154</t>
+          <t xml:space="preserve">5326332</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3170,11 +3170,11 @@
         </is>
       </c>
       <c r="H53">
-        <v>546</v>
+        <v>790</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">311853866</t>
+          <t xml:space="preserve">311853863</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3211,7 +3211,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elver Alle 4</t>
+          <t xml:space="preserve">Milnersvej 37B</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">8265582</t>
+          <t xml:space="preserve">9065689</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3230,16 +3230,16 @@
         </is>
       </c>
       <c r="H54">
-        <v>611</v>
+        <v>2588</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">311853867</t>
+          <t xml:space="preserve">311854089</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-09-05</t>
+          <t xml:space="preserve">2035-09-06</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Roskildevej 155</t>
+          <t xml:space="preserve">Milnersvej 37C</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3281,20 +3281,20 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">5331000</t>
+          <t xml:space="preserve">9065689</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H55">
-        <v>544</v>
+        <v>1820</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311854092</t>
+          <t xml:space="preserve">311854091</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selskovvej 76</t>
+          <t xml:space="preserve">Milnersvej 37D</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3341,20 +3341,20 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">5332000</t>
+          <t xml:space="preserve">9065689</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H56">
-        <v>1464</v>
+        <v>4023</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">311854090</t>
+          <t xml:space="preserve">311854093</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Milnersvej 37B</t>
+          <t xml:space="preserve">Roskildevej 155</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">9065689</t>
+          <t xml:space="preserve">5331000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3410,11 +3410,11 @@
         </is>
       </c>
       <c r="H57">
-        <v>2588</v>
+        <v>544</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">311854089</t>
+          <t xml:space="preserve">311854092</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Milnersvej 37C</t>
+          <t xml:space="preserve">Selskovvej 76</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">9065689</t>
+          <t xml:space="preserve">5332000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3470,11 +3470,11 @@
         </is>
       </c>
       <c r="H58">
-        <v>1820</v>
+        <v>1464</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">311854091</t>
+          <t xml:space="preserve">311854090</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Milnersvej 37D</t>
+          <t xml:space="preserve">Godthåbsvej 47</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3521,25 +3521,25 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">9065689</t>
+          <t xml:space="preserve">7566192</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H59">
-        <v>4023</v>
+        <v>731</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">311854093</t>
+          <t xml:space="preserve">311858077</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-09-06</t>
+          <t xml:space="preserve">2035-09-25</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trollesmindealle 27A</t>
+          <t xml:space="preserve">Højager 10</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3581,7 +3581,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">10196478</t>
+          <t xml:space="preserve">5329129</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3590,11 +3590,11 @@
         </is>
       </c>
       <c r="H60">
-        <v>702</v>
+        <v>365</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">311858081</t>
+          <t xml:space="preserve">311858079</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trollesmindealle 27</t>
+          <t xml:space="preserve">Nordre Jernbanevej 6</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3641,20 +3641,20 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">10196478</t>
+          <t xml:space="preserve">5326640</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H61">
-        <v>9576</v>
+        <v>2174</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">311858083</t>
+          <t xml:space="preserve">311858071</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -3706,11 +3706,11 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H62">
-        <v>2174</v>
+        <v>1099</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -3766,11 +3766,11 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H63">
-        <v>1099</v>
+        <v>774</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordre Jernbanevej 6</t>
+          <t xml:space="preserve">Salpetermosevej 2C</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3821,20 +3821,20 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">5326640</t>
+          <t xml:space="preserve">7964466</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H64">
-        <v>774</v>
+        <v>546</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311858071</t>
+          <t xml:space="preserve">311858076</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -3871,7 +3871,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højager 10</t>
+          <t xml:space="preserve">Trollesmindealle 27</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3881,20 +3881,20 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">5329129</t>
+          <t xml:space="preserve">10196478</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H65">
-        <v>365</v>
+        <v>9576</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311858079</t>
+          <t xml:space="preserve">311858083</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Godthåbsvej 47</t>
+          <t xml:space="preserve">Trollesmindealle 27A</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">7566192</t>
+          <t xml:space="preserve">10196478</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -3950,11 +3950,11 @@
         </is>
       </c>
       <c r="H66">
-        <v>731</v>
+        <v>702</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311858077</t>
+          <t xml:space="preserve">311858081</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -3991,7 +3991,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Salpetermosevej 2C</t>
+          <t xml:space="preserve">Brødeskovvej 54</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">7964466</t>
+          <t xml:space="preserve">2254898</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -4010,16 +4010,16 @@
         </is>
       </c>
       <c r="H67">
-        <v>546</v>
+        <v>303</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311858076</t>
+          <t xml:space="preserve">311858432</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-09-25</t>
+          <t xml:space="preserve">2035-09-26</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4051,17 +4051,17 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brødeskovvej 54</t>
+          <t xml:space="preserve">Skolevej 3</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">3400</t>
+          <t xml:space="preserve">3320</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2254898</t>
+          <t xml:space="preserve">7004638</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -4070,11 +4070,11 @@
         </is>
       </c>
       <c r="H68">
-        <v>303</v>
+        <v>2940</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311858432</t>
+          <t xml:space="preserve">311858480</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4111,30 +4111,30 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stationsvej 1</t>
+          <t xml:space="preserve">Skolevej 5</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">3400</t>
+          <t xml:space="preserve">3320</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2254961</t>
+          <t xml:space="preserve">7004638</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H69">
-        <v>299</v>
+        <v>504</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311858422</t>
+          <t xml:space="preserve">311858480</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 3</t>
+          <t xml:space="preserve">Skolevej 7</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4186,15 +4186,15 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H70">
-        <v>2940</v>
+        <v>1404</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311858480</t>
+          <t xml:space="preserve">311858483</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 5</t>
+          <t xml:space="preserve">Skolevej 7</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4246,11 +4246,11 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H71">
-        <v>504</v>
+        <v>652</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -4291,30 +4291,30 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 7</t>
+          <t xml:space="preserve">Stationsvej 1</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">3320</t>
+          <t xml:space="preserve">3400</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">7004638</t>
+          <t xml:space="preserve">2254961</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H72">
-        <v>1404</v>
+        <v>299</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311858483</t>
+          <t xml:space="preserve">311858422</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4351,35 +4351,35 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 7</t>
+          <t xml:space="preserve">Carlsbergvej 13</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">3320</t>
+          <t xml:space="preserve">3400</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">7004638</t>
+          <t xml:space="preserve">5327777</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H73">
-        <v>652</v>
+        <v>6103</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311858480</t>
+          <t xml:space="preserve">311861223</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-09-26</t>
+          <t xml:space="preserve">2035-10-10</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -4426,15 +4426,15 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="H74">
-        <v>6103</v>
+        <v>480</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311861223</t>
+          <t xml:space="preserve">311861225</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carlsbergvej 13</t>
+          <t xml:space="preserve">Carlsbergvej 13A</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4486,15 +4486,15 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H75">
-        <v>480</v>
+        <v>374</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311861225</t>
+          <t xml:space="preserve">311861224</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carlsbergvej 13A</t>
+          <t xml:space="preserve">Nysøgårdsvej 9</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -4541,20 +4541,20 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">5327777</t>
+          <t xml:space="preserve">9633243</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H76">
-        <v>374</v>
+        <v>495</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311861224</t>
+          <t xml:space="preserve">311861196</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -4606,11 +4606,11 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H77">
-        <v>495</v>
+        <v>565</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nysøgårdsvej 9</t>
+          <t xml:space="preserve">Kirsebæralle 5</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -4661,25 +4661,25 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">9633243</t>
+          <t xml:space="preserve">2301632</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H78">
-        <v>565</v>
+        <v>288</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311861196</t>
+          <t xml:space="preserve">311862715</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-10</t>
+          <t xml:space="preserve">2035-10-17</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirsebæralle 5</t>
+          <t xml:space="preserve">Milnersvej 37A</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2301632</t>
+          <t xml:space="preserve">9065626</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -4730,11 +4730,11 @@
         </is>
       </c>
       <c r="H79">
-        <v>288</v>
+        <v>385</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311862715</t>
+          <t xml:space="preserve">311862716</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -5131,17 +5131,17 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Milnersvej 37A</t>
+          <t xml:space="preserve">Maglekærvej 6</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t xml:space="preserve">3400</t>
+          <t xml:space="preserve">3330</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">9065626</t>
+          <t xml:space="preserve">9712207</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -5150,16 +5150,16 @@
         </is>
       </c>
       <c r="H86">
-        <v>385</v>
+        <v>995</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311862716</t>
+          <t xml:space="preserve">311865616</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-17</t>
+          <t xml:space="preserve">2035-10-31</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5251,17 +5251,17 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maglekærvej 6</t>
+          <t xml:space="preserve">Texasvej 5</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t xml:space="preserve">3330</t>
+          <t xml:space="preserve">3400</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">9712207</t>
+          <t xml:space="preserve">5330857</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -5270,16 +5270,16 @@
         </is>
       </c>
       <c r="H88">
-        <v>995</v>
+        <v>571</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311865616</t>
+          <t xml:space="preserve">311871335</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-31</t>
+          <t xml:space="preserve">2035-12-02</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -5311,7 +5311,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Texasvej 5</t>
+          <t xml:space="preserve">Tolvkarlevej 70</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5321,7 +5321,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">5330857</t>
+          <t xml:space="preserve">5330869</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -5330,11 +5330,11 @@
         </is>
       </c>
       <c r="H89">
-        <v>571</v>
+        <v>435</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311871335</t>
+          <t xml:space="preserve">311871336</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -5371,7 +5371,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tolvkarlevej 70</t>
+          <t xml:space="preserve">Brødeskovvej 37</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5381,25 +5381,25 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">5330869</t>
+          <t xml:space="preserve">9924661</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="H90">
-        <v>435</v>
+        <v>409</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311871336</t>
+          <t xml:space="preserve">311871443</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-02</t>
+          <t xml:space="preserve">2035-12-03</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tolvkarlevej 361</t>
+          <t xml:space="preserve">Brødeskovvej 37</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5441,20 +5441,20 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">1352718</t>
+          <t xml:space="preserve">9924661</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H91">
-        <v>734</v>
+        <v>320</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311871441</t>
+          <t xml:space="preserve">311871443</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -5491,30 +5491,30 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strøvej 96</t>
+          <t xml:space="preserve">Brødeskovvej 39</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t xml:space="preserve">3330</t>
+          <t xml:space="preserve">3400</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2246519</t>
+          <t xml:space="preserve">9924661</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H92">
-        <v>322</v>
+        <v>535</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311871450</t>
+          <t xml:space="preserve">311871443</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sophienborgvænget 6</t>
+          <t xml:space="preserve">Brødeskovvej 39</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -5561,20 +5561,20 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2301964</t>
+          <t xml:space="preserve">9924661</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H93">
-        <v>537</v>
+        <v>450</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311871491</t>
+          <t xml:space="preserve">311871443</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -5611,7 +5611,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frederiksgade 9</t>
+          <t xml:space="preserve">Brødeskovvej 39</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -5621,20 +5621,20 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">5326967</t>
+          <t xml:space="preserve">9924661</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="H94">
-        <v>616</v>
+        <v>795</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311871599</t>
+          <t xml:space="preserve">311871443</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -5671,7 +5671,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frederiksgade 11</t>
+          <t xml:space="preserve">Brødeskovvej 39</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -5681,20 +5681,20 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">5326982</t>
+          <t xml:space="preserve">9924661</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H95">
-        <v>403</v>
+        <v>1473</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311871598</t>
+          <t xml:space="preserve">311871443</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kulsviervej 20</t>
+          <t xml:space="preserve">Brødeskovvej 39</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -5741,20 +5741,20 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">5330557</t>
+          <t xml:space="preserve">9924661</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H96">
-        <v>331</v>
+        <v>587</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">311871490</t>
+          <t xml:space="preserve">311871443</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kulsviervej 20</t>
+          <t xml:space="preserve">Brødeskovvej 39</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -5801,20 +5801,20 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">5330557</t>
+          <t xml:space="preserve">9924661</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H97">
-        <v>258</v>
+        <v>1379</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311871490</t>
+          <t xml:space="preserve">311871443</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tjærebyvej 24</t>
+          <t xml:space="preserve">Frederiksgade 11</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -5861,7 +5861,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">9065569</t>
+          <t xml:space="preserve">5326982</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -5870,11 +5870,11 @@
         </is>
       </c>
       <c r="H98">
-        <v>310</v>
+        <v>403</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311871489</t>
+          <t xml:space="preserve">311871598</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -5911,30 +5911,30 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strøvej 103</t>
+          <t xml:space="preserve">Frederiksgade 9</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t xml:space="preserve">3330</t>
+          <t xml:space="preserve">3400</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">9595470</t>
+          <t xml:space="preserve">5326967</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H99">
-        <v>664</v>
+        <v>616</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311871451</t>
+          <t xml:space="preserve">311871599</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -5971,7 +5971,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brødeskovvej 39</t>
+          <t xml:space="preserve">Kulsviervej 20</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -5981,20 +5981,20 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">9924661</t>
+          <t xml:space="preserve">5330557</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H100">
-        <v>535</v>
+        <v>331</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311871443</t>
+          <t xml:space="preserve">311871490</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brødeskovvej 39</t>
+          <t xml:space="preserve">Kulsviervej 20</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6041,20 +6041,20 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">9924661</t>
+          <t xml:space="preserve">5330557</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H101">
-        <v>450</v>
+        <v>258</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311871443</t>
+          <t xml:space="preserve">311871490</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -6091,7 +6091,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brødeskovvej 39</t>
+          <t xml:space="preserve">Sophienborgvænget 6</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -6101,20 +6101,20 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">9924661</t>
+          <t xml:space="preserve">2301964</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H102">
-        <v>795</v>
+        <v>537</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311871443</t>
+          <t xml:space="preserve">311871491</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -6151,30 +6151,30 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brødeskovvej 37</t>
+          <t xml:space="preserve">Strøvej 103</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t xml:space="preserve">3400</t>
+          <t xml:space="preserve">3330</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">9924661</t>
+          <t xml:space="preserve">9595470</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H103">
-        <v>409</v>
+        <v>664</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311871443</t>
+          <t xml:space="preserve">311871451</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -6211,30 +6211,30 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brødeskovvej 39</t>
+          <t xml:space="preserve">Strøvej 96</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t xml:space="preserve">3400</t>
+          <t xml:space="preserve">3330</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">9924661</t>
+          <t xml:space="preserve">2246519</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H104">
-        <v>1473</v>
+        <v>322</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311871443</t>
+          <t xml:space="preserve">311871450</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brødeskovvej 39</t>
+          <t xml:space="preserve">Tjærebyvej 24</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -6281,20 +6281,20 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">9924661</t>
+          <t xml:space="preserve">9065569</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H105">
-        <v>587</v>
+        <v>310</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311871443</t>
+          <t xml:space="preserve">311871489</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brødeskovvej 39</t>
+          <t xml:space="preserve">Tolvkarlevej 361</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -6341,20 +6341,20 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">9924661</t>
+          <t xml:space="preserve">1352718</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H106">
-        <v>1379</v>
+        <v>734</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311871443</t>
+          <t xml:space="preserve">311871441</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brødeskovvej 37</t>
+          <t xml:space="preserve">Gadevangsvej 121</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -6401,25 +6401,25 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">9924661</t>
+          <t xml:space="preserve">2324233</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H107">
-        <v>320</v>
+        <v>412</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311871443</t>
+          <t xml:space="preserve">311871863</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-03</t>
+          <t xml:space="preserve">2035-12-04</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gadevangsvej 121</t>
+          <t xml:space="preserve">Kollerødvej 1A</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -6521,25 +6521,25 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2324233</t>
+          <t xml:space="preserve">2254877</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H109">
-        <v>412</v>
+        <v>1466</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311871863</t>
+          <t xml:space="preserve">311872068</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-04</t>
+          <t xml:space="preserve">2035-12-05</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -6631,7 +6631,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kollerødvej 1A</t>
+          <t xml:space="preserve">Grønnegade 15</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -6641,25 +6641,25 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2254877</t>
+          <t xml:space="preserve">7568565</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H111">
-        <v>1466</v>
+        <v>1448</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311872068</t>
+          <t xml:space="preserve">311872207</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-05</t>
+          <t xml:space="preserve">2035-12-08</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønnegade 15</t>
+          <t xml:space="preserve">Blytækkervej 18</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -6701,7 +6701,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">7568565</t>
+          <t xml:space="preserve">5328262, 100655352</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -6710,16 +6710,16 @@
         </is>
       </c>
       <c r="H112">
-        <v>1448</v>
+        <v>480</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311872207</t>
+          <t xml:space="preserve">311872503</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-08</t>
+          <t xml:space="preserve">2035-12-09</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -6751,17 +6751,17 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østervang 124</t>
+          <t xml:space="preserve">Byvej 14B</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t xml:space="preserve">3400</t>
+          <t xml:space="preserve">3320</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">1352718</t>
+          <t xml:space="preserve">2281030</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -6770,11 +6770,11 @@
         </is>
       </c>
       <c r="H113">
-        <v>934</v>
+        <v>394</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311872602</t>
+          <t xml:space="preserve">311872484</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østervang 126</t>
+          <t xml:space="preserve">Clausensvej 1</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -6821,20 +6821,20 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">1352718</t>
+          <t xml:space="preserve">5329897</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H114">
-        <v>840</v>
+        <v>428</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311872602</t>
+          <t xml:space="preserve">311872481</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -6871,7 +6871,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østervang 124</t>
+          <t xml:space="preserve">Clausensvej 3</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -6881,7 +6881,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">1352718</t>
+          <t xml:space="preserve">5329897</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -6890,11 +6890,11 @@
         </is>
       </c>
       <c r="H115">
-        <v>1427</v>
+        <v>380</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311872602</t>
+          <t xml:space="preserve">311872482</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -6931,7 +6931,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østervang 124</t>
+          <t xml:space="preserve">Klostervej 17</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -6941,20 +6941,20 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">1352718</t>
+          <t xml:space="preserve">5328179</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H116">
-        <v>934</v>
+        <v>575</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311872602</t>
+          <t xml:space="preserve">311872485</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -6991,7 +6991,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østervang 124</t>
+          <t xml:space="preserve">Teglværksvej 19</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -7001,20 +7001,20 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">1352718</t>
+          <t xml:space="preserve">2301858</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H117">
-        <v>1868</v>
+        <v>6286</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311872602</t>
+          <t xml:space="preserve">311872502</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -7051,7 +7051,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østervang 124</t>
+          <t xml:space="preserve">Teglværksvej 19</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -7061,20 +7061,20 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">1352718</t>
+          <t xml:space="preserve">2301858</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H118">
-        <v>1894</v>
+        <v>1330</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">311872602</t>
+          <t xml:space="preserve">311872502</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østervang 124</t>
+          <t xml:space="preserve">Teglværksvej 19</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -7121,20 +7121,20 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">1352718</t>
+          <t xml:space="preserve">2301858</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H119">
-        <v>3578</v>
+        <v>1325</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t xml:space="preserve">311872602</t>
+          <t xml:space="preserve">311872502</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -7171,7 +7171,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østervang 126</t>
+          <t xml:space="preserve">Teglværksvej 19</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -7181,20 +7181,20 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">1352718</t>
+          <t xml:space="preserve">2301858</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H120">
-        <v>1868</v>
+        <v>1647</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311872602</t>
+          <t xml:space="preserve">311872502</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -7231,30 +7231,30 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byvej 14B</t>
+          <t xml:space="preserve">Teglværksvej 19</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t xml:space="preserve">3320</t>
+          <t xml:space="preserve">3400</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2281030</t>
+          <t xml:space="preserve">2301858</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H121">
-        <v>394</v>
+        <v>2474</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311872484</t>
+          <t xml:space="preserve">311872502</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -7306,11 +7306,11 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H122">
-        <v>6286</v>
+        <v>387</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Teglværksvej 19</t>
+          <t xml:space="preserve">Østervang 124</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -7361,20 +7361,20 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2301858</t>
+          <t xml:space="preserve">1352718</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H123">
-        <v>1330</v>
+        <v>934</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311872502</t>
+          <t xml:space="preserve">311872602</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -7411,7 +7411,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Teglværksvej 19</t>
+          <t xml:space="preserve">Østervang 124</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -7421,20 +7421,20 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2301858</t>
+          <t xml:space="preserve">1352718</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H124">
-        <v>1325</v>
+        <v>1427</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311872502</t>
+          <t xml:space="preserve">311872602</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -7471,7 +7471,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Teglværksvej 19</t>
+          <t xml:space="preserve">Østervang 124</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -7481,20 +7481,20 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2301858</t>
+          <t xml:space="preserve">1352718</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H125">
-        <v>1647</v>
+        <v>934</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311872502</t>
+          <t xml:space="preserve">311872602</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Teglværksvej 19</t>
+          <t xml:space="preserve">Østervang 124</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -7541,20 +7541,20 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2301858</t>
+          <t xml:space="preserve">1352718</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H126">
-        <v>2474</v>
+        <v>1868</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311872502</t>
+          <t xml:space="preserve">311872602</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -7591,7 +7591,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Teglværksvej 19</t>
+          <t xml:space="preserve">Østervang 124</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -7601,20 +7601,20 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2301858</t>
+          <t xml:space="preserve">1352718</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H127">
-        <v>387</v>
+        <v>1894</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311872502</t>
+          <t xml:space="preserve">311872602</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klostervej 17</t>
+          <t xml:space="preserve">Østervang 124</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -7661,20 +7661,20 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">5328179</t>
+          <t xml:space="preserve">1352718</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H128">
-        <v>575</v>
+        <v>3578</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311872485</t>
+          <t xml:space="preserve">311872602</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -7711,7 +7711,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blytækkervej 18</t>
+          <t xml:space="preserve">Østervang 126</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -7721,20 +7721,20 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">5328262, 100655352</t>
+          <t xml:space="preserve">1352718</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H129">
-        <v>480</v>
+        <v>840</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311872503</t>
+          <t xml:space="preserve">311872602</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -7771,7 +7771,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Clausensvej 1</t>
+          <t xml:space="preserve">Østervang 126</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -7781,20 +7781,20 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">5329897</t>
+          <t xml:space="preserve">1352718</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H130">
-        <v>428</v>
+        <v>1868</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311872481</t>
+          <t xml:space="preserve">311872602</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -7831,7 +7831,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Clausensvej 3</t>
+          <t xml:space="preserve">Hillerødsholmsalle 2</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -7841,25 +7841,25 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">5329897</t>
+          <t xml:space="preserve">5331670</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H131">
-        <v>380</v>
+        <v>3098</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311872482</t>
+          <t xml:space="preserve">311873647</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-09</t>
+          <t xml:space="preserve">2035-12-16</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -7906,11 +7906,11 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H132">
-        <v>3098</v>
+        <v>1957</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
@@ -7966,11 +7966,11 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H133">
-        <v>1957</v>
+        <v>4724</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
@@ -8026,11 +8026,11 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H134">
-        <v>4724</v>
+        <v>2279</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
@@ -8191,7 +8191,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hillerødsholmsalle 2</t>
+          <t xml:space="preserve">Baunevej 16</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -8201,25 +8201,25 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">5331670</t>
+          <t xml:space="preserve">1307795</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H137">
-        <v>2279</v>
+        <v>278</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311873647</t>
+          <t xml:space="preserve">311874086</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-16</t>
+          <t xml:space="preserve">2035-12-17</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -8251,7 +8251,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baunevej 16</t>
+          <t xml:space="preserve">Carlsbergvej 13</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -8261,20 +8261,20 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t xml:space="preserve">1307795</t>
+          <t xml:space="preserve">5327773</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H138">
-        <v>278</v>
+        <v>1459</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874086</t>
+          <t xml:space="preserve">311874087</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -8311,7 +8311,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hulvejen 29C</t>
+          <t xml:space="preserve">Carlsbergvej 13</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -8321,20 +8321,20 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2254667</t>
+          <t xml:space="preserve">5327773</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H139">
-        <v>359</v>
+        <v>744</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874085</t>
+          <t xml:space="preserve">311874087</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -8371,7 +8371,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tulstrup Have 3</t>
+          <t xml:space="preserve">Christiansgade 1</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -8381,20 +8381,20 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2278059</t>
+          <t xml:space="preserve">5326860</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H140">
-        <v>395</v>
+        <v>1535</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874093</t>
+          <t xml:space="preserve">311874091</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fredensvej 12C</t>
+          <t xml:space="preserve">Christiansgade 1</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -8441,20 +8441,20 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">5326860</t>
+          <t xml:space="preserve">7416190</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H141">
-        <v>635</v>
+        <v>2227</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874090</t>
+          <t xml:space="preserve">311874092</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fredensvej 12B</t>
+          <t xml:space="preserve">Fredensvej 12A</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -8506,11 +8506,11 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H142">
-        <v>288</v>
+        <v>1214</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
@@ -8551,7 +8551,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fredensvej 12A</t>
+          <t xml:space="preserve">Fredensvej 12B</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -8566,11 +8566,11 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H143">
-        <v>1214</v>
+        <v>288</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christiansgade 1</t>
+          <t xml:space="preserve">Fredensvej 12C</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -8626,15 +8626,15 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H144">
-        <v>1535</v>
+        <v>635</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874091</t>
+          <t xml:space="preserve">311874090</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -8671,7 +8671,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carlsbergvej 13</t>
+          <t xml:space="preserve">Hulvejen 29C</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -8681,20 +8681,20 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">5327773</t>
+          <t xml:space="preserve">2254667</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H145">
-        <v>1459</v>
+        <v>359</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874087</t>
+          <t xml:space="preserve">311874085</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -8731,7 +8731,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carlsbergvej 13</t>
+          <t xml:space="preserve">Løngangsgade 19</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -8741,20 +8741,20 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">5327773</t>
+          <t xml:space="preserve">5333179</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H146">
-        <v>744</v>
+        <v>659</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874087</t>
+          <t xml:space="preserve">311874088</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -8791,17 +8791,17 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Løngangsgade 19</t>
+          <t xml:space="preserve">Th. Petersens Vej 23</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t xml:space="preserve">3400</t>
+          <t xml:space="preserve">3330</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">5333179</t>
+          <t xml:space="preserve">9725751</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -8810,11 +8810,11 @@
         </is>
       </c>
       <c r="H147">
-        <v>659</v>
+        <v>760</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874088</t>
+          <t xml:space="preserve">311874089</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -8851,7 +8851,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christiansgade 1</t>
+          <t xml:space="preserve">Tulstrup Have 3</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -8861,20 +8861,20 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t xml:space="preserve">7416190</t>
+          <t xml:space="preserve">2278059</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H148">
-        <v>2227</v>
+        <v>395</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874092</t>
+          <t xml:space="preserve">311874093</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -8911,17 +8911,17 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Th. Petersens Vej 23</t>
+          <t xml:space="preserve">Birkevej 25A</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t xml:space="preserve">3330</t>
+          <t xml:space="preserve">3320</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t xml:space="preserve">9725751</t>
+          <t xml:space="preserve">7629375</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -8930,16 +8930,16 @@
         </is>
       </c>
       <c r="H149">
-        <v>760</v>
+        <v>735</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874089</t>
+          <t xml:space="preserve">311874137</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-17</t>
+          <t xml:space="preserve">2035-12-18</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
@@ -8971,17 +8971,17 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kaj Sommers Vej 29</t>
+          <t xml:space="preserve">Horsevænget 48</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t xml:space="preserve">3320</t>
+          <t xml:space="preserve">3400</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t xml:space="preserve">10026444</t>
+          <t xml:space="preserve">5328509</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -8990,11 +8990,11 @@
         </is>
       </c>
       <c r="H150">
-        <v>864</v>
+        <v>931</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874136</t>
+          <t xml:space="preserve">311874133</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -9031,7 +9031,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Slangerupgade 10</t>
+          <t xml:space="preserve">Horsevænget 50</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -9041,7 +9041,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve">5326298</t>
+          <t xml:space="preserve">5328508</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -9050,11 +9050,11 @@
         </is>
       </c>
       <c r="H151">
-        <v>261</v>
+        <v>874</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874135</t>
+          <t xml:space="preserve">311874134</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -9091,7 +9091,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Horsevænget 50</t>
+          <t xml:space="preserve">Højager 112</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -9101,7 +9101,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t xml:space="preserve">5328508</t>
+          <t xml:space="preserve">9065650</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -9110,11 +9110,11 @@
         </is>
       </c>
       <c r="H152">
-        <v>874</v>
+        <v>366</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874134</t>
+          <t xml:space="preserve">311874139</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -9151,17 +9151,17 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Horsevænget 48</t>
+          <t xml:space="preserve">Kaj Sommers Vej 29</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t xml:space="preserve">3400</t>
+          <t xml:space="preserve">3320</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t xml:space="preserve">5328509</t>
+          <t xml:space="preserve">10026444</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -9170,11 +9170,11 @@
         </is>
       </c>
       <c r="H153">
-        <v>931</v>
+        <v>864</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874133</t>
+          <t xml:space="preserve">311874136</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygade 12</t>
+          <t xml:space="preserve">Ny Harløsevej 26A</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -9221,20 +9221,20 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t xml:space="preserve">7004602</t>
+          <t xml:space="preserve">7629375</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H154">
-        <v>1119</v>
+        <v>310</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874138</t>
+          <t xml:space="preserve">311874137</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -9286,11 +9286,11 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H155">
-        <v>570</v>
+        <v>1119</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
@@ -9346,11 +9346,11 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H156">
-        <v>456</v>
+        <v>570</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
@@ -9391,7 +9391,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birkevej 25A</t>
+          <t xml:space="preserve">Nygade 12</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -9401,20 +9401,20 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">7629375</t>
+          <t xml:space="preserve">7004602</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H157">
-        <v>735</v>
+        <v>456</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874137</t>
+          <t xml:space="preserve">311874138</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -9451,30 +9451,30 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ny Harløsevej 26A</t>
+          <t xml:space="preserve">Slangerupgade 10</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t xml:space="preserve">3320</t>
+          <t xml:space="preserve">3400</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t xml:space="preserve">7629375</t>
+          <t xml:space="preserve">5326298</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H158">
-        <v>310</v>
+        <v>261</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874137</t>
+          <t xml:space="preserve">311874135</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -9511,7 +9511,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højager 112</t>
+          <t xml:space="preserve">Gadevangsvej 145B</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -9521,7 +9521,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t xml:space="preserve">9065650</t>
+          <t xml:space="preserve">2325409</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -9530,16 +9530,16 @@
         </is>
       </c>
       <c r="H159">
-        <v>366</v>
+        <v>334</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874139</t>
+          <t xml:space="preserve">311874645</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-18</t>
+          <t xml:space="preserve">2035-12-19</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
@@ -9571,7 +9571,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ullerødvej 44</t>
+          <t xml:space="preserve">Kornvænget 10</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2301750</t>
+          <t xml:space="preserve">5329171</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -9590,11 +9590,11 @@
         </is>
       </c>
       <c r="H160">
-        <v>356</v>
+        <v>257</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874648</t>
+          <t xml:space="preserve">311874644</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -9631,7 +9631,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gadevangsvej 145B</t>
+          <t xml:space="preserve">Rønnevangsalle 3</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -9641,20 +9641,20 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2325409</t>
+          <t xml:space="preserve">5333853</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H161">
-        <v>334</v>
+        <v>1392</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874645</t>
+          <t xml:space="preserve">311874646</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -9691,7 +9691,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kornvænget 10</t>
+          <t xml:space="preserve">Skansevej 20A</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -9701,7 +9701,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t xml:space="preserve">5329171</t>
+          <t xml:space="preserve">5330379</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -9710,11 +9710,11 @@
         </is>
       </c>
       <c r="H162">
-        <v>257</v>
+        <v>458</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874644</t>
+          <t xml:space="preserve">311874647</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -9751,7 +9751,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skansevej 20A</t>
+          <t xml:space="preserve">Ullerødvej 44</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -9761,7 +9761,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t xml:space="preserve">5330379</t>
+          <t xml:space="preserve">2301750</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -9770,11 +9770,11 @@
         </is>
       </c>
       <c r="H163">
-        <v>458</v>
+        <v>356</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874647</t>
+          <t xml:space="preserve">311874648</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rønnevangsalle 3</t>
+          <t xml:space="preserve">Lindevej 3</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -9821,25 +9821,25 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t xml:space="preserve">5333853</t>
+          <t xml:space="preserve">5327108</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H164">
-        <v>1392</v>
+        <v>847</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874646</t>
+          <t xml:space="preserve">311875278</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-19</t>
+          <t xml:space="preserve">2036-01-06</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
@@ -9871,7 +9871,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Slangerupgade 60</t>
+          <t xml:space="preserve">Lindevej 5</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -9881,20 +9881,20 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t xml:space="preserve">1352822</t>
+          <t xml:space="preserve">5327108</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H165">
-        <v>360</v>
+        <v>640</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875283</t>
+          <t xml:space="preserve">311875278</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -9931,7 +9931,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindevej 3</t>
+          <t xml:space="preserve">Milnersvej 35C</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -9941,7 +9941,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t xml:space="preserve">5327108</t>
+          <t xml:space="preserve">5328529</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -9950,11 +9950,11 @@
         </is>
       </c>
       <c r="H166">
-        <v>847</v>
+        <v>5038</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875278</t>
+          <t xml:space="preserve">311875280</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -9991,7 +9991,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindevej 5</t>
+          <t xml:space="preserve">Slangerupgade 60</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -10001,20 +10001,20 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t xml:space="preserve">5327108</t>
+          <t xml:space="preserve">1352822</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H167">
-        <v>640</v>
+        <v>360</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875278</t>
+          <t xml:space="preserve">311875283</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -10051,7 +10051,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Milnersvej 35C</t>
+          <t xml:space="preserve">Klostervej 26</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -10061,7 +10061,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t xml:space="preserve">5328529</t>
+          <t xml:space="preserve">5326297</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -10070,16 +10070,16 @@
         </is>
       </c>
       <c r="H168">
-        <v>5038</v>
+        <v>431</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875280</t>
+          <t xml:space="preserve">311875479</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-01-06</t>
+          <t xml:space="preserve">2036-01-07</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
@@ -10111,7 +10111,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nonnebuen 1</t>
+          <t xml:space="preserve">Lindevej 2</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -10121,7 +10121,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t xml:space="preserve">10130052</t>
+          <t xml:space="preserve">5327094</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -10130,11 +10130,11 @@
         </is>
       </c>
       <c r="H169">
-        <v>1306</v>
+        <v>283</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875473</t>
+          <t xml:space="preserve">311875481</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -10171,17 +10171,17 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strøvej 107</t>
+          <t xml:space="preserve">Nonnebuen 1</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t xml:space="preserve">3330</t>
+          <t xml:space="preserve">3400</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2246500</t>
+          <t xml:space="preserve">10130052</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -10190,11 +10190,11 @@
         </is>
       </c>
       <c r="H170">
-        <v>585</v>
+        <v>1306</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875477</t>
+          <t xml:space="preserve">311875473</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
@@ -10231,30 +10231,30 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strøvej 105</t>
+          <t xml:space="preserve">Ny Harløsevej 24</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t xml:space="preserve">3330</t>
+          <t xml:space="preserve">3320</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2246500</t>
+          <t xml:space="preserve">7004605</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H171">
-        <v>1205</v>
+        <v>5933</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875477</t>
+          <t xml:space="preserve">311875476</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -10291,30 +10291,30 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strøvej 105</t>
+          <t xml:space="preserve">Rønnevangsalle 5</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t xml:space="preserve">3330</t>
+          <t xml:space="preserve">3400</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2246500</t>
+          <t xml:space="preserve">5333967</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H172">
-        <v>272</v>
+        <v>1670</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875477</t>
+          <t xml:space="preserve">311875474</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -10351,30 +10351,30 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Uvelse Byvej 3</t>
+          <t xml:space="preserve">Rønnevangsalle 5</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t xml:space="preserve">3550</t>
+          <t xml:space="preserve">3400</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t xml:space="preserve">2261352</t>
+          <t xml:space="preserve">5333967</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H173">
-        <v>956</v>
+        <v>1318</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875478</t>
+          <t xml:space="preserve">311875475</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -10411,17 +10411,17 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Uvelse Byvej 3</t>
+          <t xml:space="preserve">Strøvej 105</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t xml:space="preserve">3550</t>
+          <t xml:space="preserve">3330</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2261352</t>
+          <t xml:space="preserve">2246500</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -10430,11 +10430,11 @@
         </is>
       </c>
       <c r="H174">
-        <v>1059</v>
+        <v>1205</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875478</t>
+          <t xml:space="preserve">311875477</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -10471,30 +10471,30 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klostervej 26</t>
+          <t xml:space="preserve">Strøvej 105</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t xml:space="preserve">3400</t>
+          <t xml:space="preserve">3330</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t xml:space="preserve">5326297</t>
+          <t xml:space="preserve">2246500</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H175">
-        <v>431</v>
+        <v>272</v>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875479</t>
+          <t xml:space="preserve">311875477</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -10531,17 +10531,17 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindevej 2</t>
+          <t xml:space="preserve">Strøvej 107</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t xml:space="preserve">3400</t>
+          <t xml:space="preserve">3330</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t xml:space="preserve">5327094</t>
+          <t xml:space="preserve">2246500</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -10550,11 +10550,11 @@
         </is>
       </c>
       <c r="H176">
-        <v>283</v>
+        <v>585</v>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875481</t>
+          <t xml:space="preserve">311875477</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -10591,30 +10591,30 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rønnevangsalle 5</t>
+          <t xml:space="preserve">Uvelse Byvej 3</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t xml:space="preserve">3400</t>
+          <t xml:space="preserve">3550</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t xml:space="preserve">5333967</t>
+          <t xml:space="preserve">2261352</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H177">
-        <v>1670</v>
+        <v>956</v>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875474</t>
+          <t xml:space="preserve">311875478</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -10651,30 +10651,30 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rønnevangsalle 5</t>
+          <t xml:space="preserve">Uvelse Byvej 3</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t xml:space="preserve">3400</t>
+          <t xml:space="preserve">3550</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t xml:space="preserve">5333967</t>
+          <t xml:space="preserve">2261352</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H178">
-        <v>1318</v>
+        <v>1059</v>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875475</t>
+          <t xml:space="preserve">311875478</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -10711,17 +10711,17 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ny Harløsevej 24</t>
+          <t xml:space="preserve">Smedievej 1</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t xml:space="preserve">3320</t>
+          <t xml:space="preserve">3400</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t xml:space="preserve">7004605</t>
+          <t xml:space="preserve">5330767</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -10730,16 +10730,16 @@
         </is>
       </c>
       <c r="H179">
-        <v>5933</v>
+        <v>360</v>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875476</t>
+          <t xml:space="preserve">311879987</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-01-07</t>
+          <t xml:space="preserve">2036-02-02</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
@@ -10771,7 +10771,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smedievej 1</t>
+          <t xml:space="preserve">Sophienborg Alle 11</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -10781,20 +10781,20 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t xml:space="preserve">5330767</t>
+          <t xml:space="preserve">9065587</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H180">
-        <v>360</v>
+        <v>3090</v>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311879987</t>
+          <t xml:space="preserve">311879989</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -10831,7 +10831,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sophienborg Alle 9</t>
+          <t xml:space="preserve">Sophienborg Alle 7</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -10846,11 +10846,11 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H181">
-        <v>987</v>
+        <v>1764</v>
       </c>
       <c r="I181" t="inlineStr">
         <is>
@@ -10906,11 +10906,11 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="H182">
-        <v>1764</v>
+        <v>2249</v>
       </c>
       <c r="I182" t="inlineStr">
         <is>
@@ -10966,15 +10966,15 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="H183">
-        <v>2249</v>
+        <v>1768</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311879989</t>
+          <t xml:space="preserve">311879988</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
@@ -11026,15 +11026,15 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H184">
-        <v>1768</v>
+        <v>441</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311879988</t>
+          <t xml:space="preserve">311879989</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -11071,7 +11071,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sophienborg Alle 7</t>
+          <t xml:space="preserve">Sophienborg Alle 9</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -11086,11 +11086,11 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H185">
-        <v>441</v>
+        <v>987</v>
       </c>
       <c r="I185" t="inlineStr">
         <is>
@@ -11131,7 +11131,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sophienborg Alle 11</t>
+          <t xml:space="preserve">Skansevej 15A</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -11141,25 +11141,25 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t xml:space="preserve">9065587</t>
+          <t xml:space="preserve">5330163</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H186">
-        <v>3090</v>
+        <v>554</v>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311879989</t>
+          <t xml:space="preserve">311880018</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-02-02</t>
+          <t xml:space="preserve">2036-02-03</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
@@ -11191,7 +11191,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skansevej 15A</t>
+          <t xml:space="preserve">Godthåbsvej 35</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -11201,7 +11201,7 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t xml:space="preserve">5330163</t>
+          <t xml:space="preserve">5327801</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -11210,16 +11210,16 @@
         </is>
       </c>
       <c r="H187">
-        <v>554</v>
+        <v>392</v>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311880018</t>
+          <t xml:space="preserve">311880342</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-02-03</t>
+          <t xml:space="preserve">2036-02-04</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
@@ -11251,17 +11251,17 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hulvejen 29B</t>
+          <t xml:space="preserve">Gørløsevej 4</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t xml:space="preserve">3400</t>
+          <t xml:space="preserve">3550</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t xml:space="preserve">2254669</t>
+          <t xml:space="preserve">2261587</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -11270,11 +11270,11 @@
         </is>
       </c>
       <c r="H188">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311880347</t>
+          <t xml:space="preserve">311880341</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -11311,17 +11311,17 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gørløsevej 4</t>
+          <t xml:space="preserve">Hovedgaden 16C</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t xml:space="preserve">3550</t>
+          <t xml:space="preserve">3320</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t xml:space="preserve">2261587</t>
+          <t xml:space="preserve">2289366</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -11330,11 +11330,11 @@
         </is>
       </c>
       <c r="H189">
-        <v>424</v>
+        <v>743</v>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311880341</t>
+          <t xml:space="preserve">311880350</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
@@ -11371,17 +11371,17 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kornvænget 27</t>
+          <t xml:space="preserve">Hulvejen 29B</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t xml:space="preserve">3550</t>
+          <t xml:space="preserve">3400</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t xml:space="preserve">2261594</t>
+          <t xml:space="preserve">2254669</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -11390,11 +11390,11 @@
         </is>
       </c>
       <c r="H190">
-        <v>464</v>
+        <v>421</v>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t xml:space="preserve">311880338</t>
+          <t xml:space="preserve">311880347</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -11431,17 +11431,17 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 16C</t>
+          <t xml:space="preserve">Kirsebæralle 1B</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t xml:space="preserve">3320</t>
+          <t xml:space="preserve">3400</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t xml:space="preserve">2289366</t>
+          <t xml:space="preserve">2301595</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -11450,11 +11450,11 @@
         </is>
       </c>
       <c r="H191">
-        <v>743</v>
+        <v>437</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t xml:space="preserve">311880350</t>
+          <t xml:space="preserve">311880344</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -11491,17 +11491,17 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirsebæralle 1B</t>
+          <t xml:space="preserve">Kornvænget 27</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t xml:space="preserve">3400</t>
+          <t xml:space="preserve">3550</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t xml:space="preserve">2301595</t>
+          <t xml:space="preserve">2261594</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
@@ -11510,11 +11510,11 @@
         </is>
       </c>
       <c r="H192">
-        <v>437</v>
+        <v>464</v>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t xml:space="preserve">311880344</t>
+          <t xml:space="preserve">311880338</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
@@ -11551,7 +11551,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vibekevej 12</t>
+          <t xml:space="preserve">Nordstensvej 1</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -11561,7 +11561,7 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t xml:space="preserve">5326770</t>
+          <t xml:space="preserve">257561</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -11570,11 +11570,11 @@
         </is>
       </c>
       <c r="H193">
-        <v>395</v>
+        <v>1949</v>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311880346</t>
+          <t xml:space="preserve">311880345</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
@@ -11671,7 +11671,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Godthåbsvej 35</t>
+          <t xml:space="preserve">Vibekevej 12</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -11681,7 +11681,7 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t xml:space="preserve">5327801</t>
+          <t xml:space="preserve">5326770</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
@@ -11690,11 +11690,11 @@
         </is>
       </c>
       <c r="H195">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t xml:space="preserve">311880342</t>
+          <t xml:space="preserve">311880346</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">

--- a/public/exports/29189366.xlsx
+++ b/public/exports/29189366.xlsx
@@ -1674,7 +1674,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">311769699</t>
+          <t xml:space="preserve">311769701</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">311809064</t>
+          <t xml:space="preserve">311809066</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">311809060</t>
+          <t xml:space="preserve">311809066</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">311809061</t>
+          <t xml:space="preserve">311809066</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -6294,7 +6294,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311871489</t>
+          <t xml:space="preserve">311871487</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">

--- a/public/exports/29189366.xlsx
+++ b/public/exports/29189366.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L197"/>
+  <dimension ref="A1:M197"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -59,15 +59,20 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimærkningsfirma</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -124,10 +129,15 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -184,10 +194,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -244,10 +259,15 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -304,10 +324,15 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -364,10 +389,15 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -424,10 +454,15 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -484,10 +519,15 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -544,10 +584,15 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -604,10 +649,15 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -664,10 +714,15 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -724,10 +779,15 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -784,10 +844,15 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -844,10 +909,15 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -904,10 +974,15 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -964,10 +1039,15 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1024,10 +1104,15 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1079,15 +1164,20 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
+          <t xml:space="preserve">Grontmij A/S</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
           <t xml:space="preserve">2022-01-08</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1139,15 +1229,20 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kelstrupgaard VVS &amp; Ingeniør ApS</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-01-03</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1199,15 +1294,20 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kelstrupgaard VVS &amp; Ingeniør ApS</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-01-05</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1259,15 +1359,20 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-01-23</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1319,15 +1424,20 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
+          <t xml:space="preserve">KHB Consult</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-01-25</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1379,15 +1489,20 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kelstrupgaard VVS &amp; Ingeniør ApS</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-03-15</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1439,15 +1554,20 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-30</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1499,15 +1619,20 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lantner Consult ApS</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-01-04</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1559,15 +1684,20 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
+          <t xml:space="preserve">JDM Rådgivende Ingeniør ApS</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-05-30</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1619,15 +1749,20 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
+          <t xml:space="preserve">SMER Energi ApS</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-27</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1674,20 +1809,25 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">311769701</t>
+          <t xml:space="preserve">311769699</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
+          <t xml:space="preserve">SMER Energi ApS</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-27</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1739,15 +1879,20 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tæthedskompagniet ApS</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-11-04</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1799,15 +1944,20 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-01-31</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1859,15 +2009,20 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-01-31</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1919,15 +2074,20 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-01-31</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1979,15 +2139,20 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-01-31</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2039,15 +2204,20 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-01-31</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2099,15 +2269,20 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-07-03</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2159,15 +2334,20 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-07-03</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2219,15 +2399,20 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-07-03</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2279,15 +2464,20 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-07-03</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2339,15 +2529,20 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-07-03</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2399,15 +2594,20 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-07-03</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2459,15 +2659,20 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-07-03</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2519,15 +2724,20 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-07-03</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2579,15 +2789,20 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-07-03</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2639,15 +2854,20 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-07-23</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2699,15 +2919,20 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiOptimo ApS</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-08-27</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2759,15 +2984,20 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiOptimo ApS</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-08-27</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2819,15 +3049,20 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiOptimo ApS</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-08-27</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2879,15 +3114,20 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-09-05</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2939,15 +3179,20 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-09-05</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2999,15 +3244,20 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-09-05</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3059,15 +3309,20 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-09-05</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3119,15 +3374,20 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-09-05</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3179,15 +3439,20 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-09-05</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3239,15 +3504,20 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-09-06</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3299,15 +3569,20 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-09-06</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3359,15 +3634,20 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-09-06</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3419,15 +3699,20 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-09-06</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3479,15 +3764,20 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-09-06</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3539,15 +3829,20 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-09-25</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3599,15 +3894,20 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-09-25</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3659,15 +3959,20 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-09-25</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3719,15 +4024,20 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-09-25</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3779,15 +4089,20 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-09-25</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3839,15 +4154,20 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-09-25</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3899,15 +4219,20 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-09-25</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3959,15 +4284,20 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-09-25</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4019,15 +4349,20 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-09-26</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4079,15 +4414,20 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-09-26</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4139,15 +4479,20 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-09-26</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4199,15 +4544,20 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-09-26</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4259,15 +4609,20 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-09-26</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4319,15 +4674,20 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-09-26</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4379,15 +4739,20 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-10-10</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4439,15 +4804,20 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-10-10</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4499,15 +4869,20 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-10-10</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4559,15 +4934,20 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-10-10</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4619,15 +4999,20 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-10-10</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4679,15 +5064,20 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-10-17</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4739,15 +5129,20 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-10-17</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4799,15 +5194,20 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-10-17</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4859,15 +5259,20 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-10-17</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4919,15 +5324,20 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-10-17</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4979,15 +5389,20 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-10-17</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5039,15 +5454,20 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-10-17</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5099,15 +5519,20 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-10-17</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5159,15 +5584,20 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-10-31</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5219,15 +5649,20 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-10-31</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5279,15 +5714,20 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-02</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5339,15 +5779,20 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-02</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5399,15 +5844,20 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-03</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5459,15 +5909,20 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-03</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5519,15 +5974,20 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-03</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5579,15 +6039,20 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-03</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5639,15 +6104,20 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-03</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5699,15 +6169,20 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-03</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5759,15 +6234,20 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-03</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5819,15 +6299,20 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-03</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5879,15 +6364,20 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-03</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5939,15 +6429,20 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-03</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5999,15 +6494,20 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-03</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6059,15 +6559,20 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-03</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6119,15 +6624,20 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-03</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6179,15 +6689,20 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-03</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6239,15 +6754,20 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-03</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6299,15 +6819,20 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-03</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6359,15 +6884,20 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-03</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6419,15 +6949,20 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-04</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6479,15 +7014,20 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-04</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6539,15 +7079,20 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-05</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6599,15 +7144,20 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-05</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6659,15 +7209,20 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-08</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6719,15 +7274,20 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-09</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6779,15 +7339,20 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-09</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6839,15 +7404,20 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-09</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6899,15 +7469,20 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-09</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6959,15 +7534,20 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-09</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7019,15 +7599,20 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-09</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7079,15 +7664,20 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-09</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7139,15 +7729,20 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-09</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7199,15 +7794,20 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-09</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7259,15 +7859,20 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-09</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7319,15 +7924,20 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-09</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7379,15 +7989,20 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-09</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7439,15 +8054,20 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-09</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7499,15 +8119,20 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-09</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7559,15 +8184,20 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-09</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7619,15 +8249,20 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-09</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7679,15 +8314,20 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-09</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7739,15 +8379,20 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-09</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7799,15 +8444,20 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-09</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7859,15 +8509,20 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-16</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7919,15 +8574,20 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-16</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7979,15 +8639,20 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-16</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8039,15 +8704,20 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-16</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8099,15 +8769,20 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-16</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8159,15 +8834,20 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-16</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8219,15 +8899,20 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-17</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8279,15 +8964,20 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-17</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8339,15 +9029,20 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-17</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8399,15 +9094,20 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-17</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8459,15 +9159,20 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-17</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8519,15 +9224,20 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-17</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8579,15 +9289,20 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-17</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8639,15 +9354,20 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-17</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8699,15 +9419,20 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-17</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8759,15 +9484,20 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-17</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8819,15 +9549,20 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-17</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8879,15 +9614,20 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-17</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8939,15 +9679,20 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-18</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8999,15 +9744,20 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-18</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9059,15 +9809,20 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-18</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9119,15 +9874,20 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-18</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9179,15 +9939,20 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-18</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9239,15 +10004,20 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-18</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9299,15 +10069,20 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-18</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9359,15 +10134,20 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-18</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9419,15 +10199,20 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-18</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9479,15 +10264,20 @@
       </c>
       <c r="J158" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-18</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9539,15 +10329,20 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-19</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9599,15 +10394,20 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-19</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9659,15 +10459,20 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-19</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9719,15 +10524,20 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-19</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9779,15 +10589,20 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-19</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9839,15 +10654,20 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-06</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9899,15 +10719,20 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-06</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9959,15 +10784,20 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-06</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10019,15 +10849,20 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-06</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10079,15 +10914,20 @@
       </c>
       <c r="J168" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-07</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10139,15 +10979,20 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-07</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10199,15 +11044,20 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-07</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10259,15 +11109,20 @@
       </c>
       <c r="J171" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-07</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10319,15 +11174,20 @@
       </c>
       <c r="J172" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-07</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10379,15 +11239,20 @@
       </c>
       <c r="J173" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-07</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10439,15 +11304,20 @@
       </c>
       <c r="J174" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-07</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10499,15 +11369,20 @@
       </c>
       <c r="J175" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-07</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10559,15 +11434,20 @@
       </c>
       <c r="J176" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-07</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10619,15 +11499,20 @@
       </c>
       <c r="J177" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-07</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10679,15 +11564,20 @@
       </c>
       <c r="J178" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-07</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10739,15 +11629,20 @@
       </c>
       <c r="J179" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-02-02</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10799,15 +11694,20 @@
       </c>
       <c r="J180" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-02-02</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10859,15 +11759,20 @@
       </c>
       <c r="J181" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-02-02</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10919,15 +11824,20 @@
       </c>
       <c r="J182" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-02-02</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10979,15 +11889,20 @@
       </c>
       <c r="J183" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-02-02</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11039,15 +11954,20 @@
       </c>
       <c r="J184" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-02-02</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11099,15 +12019,20 @@
       </c>
       <c r="J185" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-02-02</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11159,15 +12084,20 @@
       </c>
       <c r="J186" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-02-03</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11219,15 +12149,20 @@
       </c>
       <c r="J187" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-02-04</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11279,15 +12214,20 @@
       </c>
       <c r="J188" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-02-04</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11339,15 +12279,20 @@
       </c>
       <c r="J189" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-02-04</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11399,15 +12344,20 @@
       </c>
       <c r="J190" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-02-04</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11459,15 +12409,20 @@
       </c>
       <c r="J191" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-02-04</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11519,15 +12474,20 @@
       </c>
       <c r="J192" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-02-04</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11579,15 +12539,20 @@
       </c>
       <c r="J193" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-02-04</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11639,15 +12604,20 @@
       </c>
       <c r="J194" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-02-04</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11699,15 +12669,20 @@
       </c>
       <c r="J195" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-02-04</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11759,15 +12734,20 @@
       </c>
       <c r="J196" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-02-04</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11819,21 +12799,26 @@
       </c>
       <c r="J197" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-02-17</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L197" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L197"/>
+  <autoFilter ref="A1:M197"/>
 </worksheet>
 </file>
--- a/public/exports/29189366.xlsx
+++ b/public/exports/29189366.xlsx
@@ -1939,7 +1939,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">311809066</t>
+          <t xml:space="preserve">311809064</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">311809066</t>
+          <t xml:space="preserve">311809060</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">311809066</t>
+          <t xml:space="preserve">311809061</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
